--- a/stories/arbres/TREE-DIF-008.xlsx
+++ b/stories/arbres/TREE-DIF-008.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kenzo est au marché, avec papa. Maman tient le panier. Kenzo veut inviter un copain. Le copain peut dire non. Papa dit : on propose. On peut accepter plusieurs réponses. On joue ensemble si l'autre veut. On peut jouer ensemble.</t>
+          <t>Kenzo est au marché, avec papa. Maman tient le panier. Kenzo veut inviter un copain. Le copain peut dire non. On propose. On peut accepter plusieurs réponses. On joue ensemble si l'autre veut. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo est au marché, avec papa. Maman tient le panier. Kenzo veut inviter un copain. Le copain peut dire non.
+papa|On propose. On peut accepter plusieurs réponses. On joue ensemble si l'autre veut. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1510,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1539,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Kenzo voit le train du marché, un petit train en bois. Il propose à Tom : tu viens ? Tom dit non. Kenzo accepte. On propose. On peut accepter plusieurs réponses. Papa dit : plus tard, c'est possible. On peut jouer ensemble.</t>
+          <t>Kenzo voit le train du marché, un petit train en bois. Il propose à Tom : tu viens ? Tom dit non. Kenzo accepte. On propose. On peut accepter plusieurs réponses. Plus tard, c'est possible. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1677,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo voit le train du marché, un petit train en bois. Il propose à Tom : tu viens ? Tom dit non. Kenzo accepte. On propose. On peut accepter plusieurs réponses.
+papa|Plus tard, c'est possible. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1859,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On propose sans forcer ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2032,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On propose. On accepte plusieurs réponses. Kenzo respire. Papa est là. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2181,6 +2225,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2345,6 +2394,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Près du train, Kenzo propose à Tom : on joue le matin ? Tom dit non. Kenzo accepte plusieurs réponses. Papa montre le geste, lentement. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2585,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2752,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le train. Puis Tom. Puis le matin. Le sol est un peu froid. Kenzo boit une gorgée d'eau. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2919,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3086,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'arrête près de après la sieste. Tom est rangé. Un crochet tient bien le manteau. Kenzo montre après la sieste à papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3253,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3420,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo se souvient de le train. Et de Tom. Et de le soir. Une chaussette est encore sablée. Kenzo pose Tom à sa place. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3587,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3527,7 +3616,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Près du train, Kenzo propose à Tom : après la sieste ? Tom dit : je regarde. Kenzo accepte plusieurs réponses. Papa dit : je suis là. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>Près du train, Kenzo propose à Tom : après la sieste ? Je regarde. Kenzo accepte plusieurs réponses. Je suis là. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3665,6 +3754,14 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Près du train, Kenzo propose à Tom : après la sieste ?
+enfant-m|Je regarde.
+narrateur|Kenzo accepte plusieurs réponses.
+papa|Je suis là. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3948,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4115,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le matin. Après Léa. Près de le train. Kenzo s'arrête. Il y a des miettes sur la table. Kenzo s'assoit près de papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4282,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4449,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo range Léa. après la sieste reste près de le train. Un vélo passe au loin. Kenzo raccroche un linge. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4616,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4523,7 +4645,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>le soir est là. Léa aussi. le train reste dans le souvenir. Ça sent le pain chaud. Kenzo range encore un peu, près de papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Le soir est là. Léa aussi. le train reste dans le souvenir. Ça sent le pain chaud. Kenzo range encore un peu, près de papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4661,6 +4783,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir est là. Léa aussi. le train reste dans le souvenir. Ça sent le pain chaud. Kenzo range encore un peu, près de papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4950,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4847,7 +4979,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Près du train, Kenzo propose à Tom : le soir ? Tom dit : plus tard. Kenzo accepte plusieurs réponses. Papa reste tout près. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>Près du train, Kenzo propose à Tom : le soir ? Plus tard. Kenzo accepte plusieurs réponses. Papa reste tout près. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -4985,6 +5117,13 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Près du train, Kenzo propose à Tom : le soir ?
+enfant-m|Plus tard.
+narrateur|Kenzo accepte plusieurs réponses. Papa reste tout près. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5310,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5477,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le matin. Sami est rangé. le train est fini. On attend son tour. Kenzo tend le matin à maman. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5644,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5811,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Près de après la sieste. Kenzo pose Sami. le train est derrière. Un ruban reste dans la poche. Kenzo caresse le doudou. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5978,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6145,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo montre le soir. Papa a vu le train. Et Sami. Les chaussures font toc toc. Kenzo ferme la porte, tout doux. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6312,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6167,7 +6341,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Kenzo voit le bus s'arrêter. Il propose à Léa : tu viens voir ? Léa dit : je regarde. Kenzo accepte. On propose. On peut accepter plusieurs réponses. Maman tient le panier. On peut jouer ensemble.</t>
+          <t>Kenzo voit le bus s'arrêter. Il propose à Léa : tu viens voir ? Je regarde. Kenzo accepte. On propose. On peut accepter plusieurs réponses. Maman tient le panier. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6305,6 +6479,13 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo voit le bus s'arrêter. Il propose à Léa : tu viens voir ?
+enfant-f|Je regarde.
+narrateur|Kenzo accepte. On propose. On peut accepter plusieurs réponses. Maman tient le panier. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6481,6 +6662,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On accepte plusieurs réponses ?</t>
         </is>
       </c>
     </row>
@@ -6649,6 +6835,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On propose. On accepte plusieurs réponses. Kenzo retient le geste. Papa sourit. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6839,6 +7030,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6863,7 +7059,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Près du bus, Kenzo propose à Léa : le matin ? Léa dit oui. Kenzo propose, sans forcer. Papa dit : je suis là. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>Près du bus, Kenzo propose à Léa : le matin ? Léa dit oui. Kenzo propose, sans forcer. Je suis là. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7001,6 +7197,12 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Près du bus, Kenzo propose à Léa : le matin ? Léa dit oui. Kenzo propose, sans forcer.
+papa|Je suis là. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7389,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7349,6 +7556,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le bus. Puis Tom. Puis le matin. On souffle doucement. Kenzo dit merci à papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7723,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7890,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'arrête près de après la sieste. Tom est rangé. On range un objet. Kenzo serre la main de papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8057,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8224,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo se souvient de le bus. Et de Tom. Et de le soir. Un chat miaule une fois. Kenzo prend la main de papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8391,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8558,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Près du bus, Kenzo propose à Léa : après la sieste ? Léa dit non. Kenzo accepte plusieurs réponses. Papa reste tout près. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8749,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8916,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le matin. Après Léa. Près de le bus. Kenzo s'arrête. Un linge sèche à l'air. Kenzo enfile ses chaussons. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9083,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9250,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo range Léa. après la sieste reste près de le bus. La couverture est douce. Kenzo souffle, puis sourit à papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9417,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9179,7 +9446,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>le soir est là. Léa aussi. le bus reste dans le souvenir. Le vent est doux. Kenzo range le bus dans sa tête, comme un souvenir. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Le soir est là. Léa aussi. le bus reste dans le souvenir. Le vent est doux. Kenzo range le bus dans sa tête, comme un souvenir. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9317,6 +9584,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir est là. Léa aussi. le bus reste dans le souvenir. Le vent est doux. Kenzo range le bus dans sa tête, comme un souvenir. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9751,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9503,7 +9780,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Près du bus, Kenzo propose à Léa : le soir ? Léa dit : je regarde. Kenzo accepte plusieurs réponses. Papa montre le geste, lentement. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>Près du bus, Kenzo propose à Léa : le soir ? Je regarde. Kenzo accepte plusieurs réponses. Papa montre le geste, lentement. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9641,6 +9918,13 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Près du bus, Kenzo propose à Léa : le soir ?
+enfant-f|Je regarde.
+narrateur|Kenzo accepte plusieurs réponses. Papa montre le geste, lentement. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10111,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9989,6 +10278,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le matin. Sami est rangé. le bus est fini. La lumière est claire. Maman n'est pas loin. Kenzo les rejoint. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10445,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10175,7 +10474,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Près de après la sieste. Kenzo pose Sami. le bus est derrière. Un galet est encore chaud. Kenzo dit : j'ai appris. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Près de après la sieste. Kenzo pose Sami. le bus est derrière. Un galet est encore chaud. J'ai appris. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10313,6 +10612,13 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Près de après la sieste. Kenzo pose Sami. le bus est derrière. Un galet est encore chaud.
+enfant-m|J'ai appris. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard.
+narrateur|Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10781,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10637,6 +10948,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo montre le soir. Papa a vu le bus. Et Sami. Une cloche tinte, tout loin. Kenzo plie un pull. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11115,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10823,7 +11144,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Kenzo s'approche de la voiture de courses, un jouet. Il propose à Sami : on joue ? Sami dit : plus tard. Kenzo accepte. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>Kenzo s'approche de la voiture de courses, un jouet. Il propose à Sami : on joue ? Plus tard. Kenzo accepte. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10961,6 +11282,13 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de la voiture de courses, un jouet. Il propose à Sami : on joue ?
+enfant-m|Plus tard.
+narrateur|Kenzo accepte. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11137,6 +11465,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On invite, et après ?</t>
         </is>
       </c>
     </row>
@@ -11305,6 +11638,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On propose. On accepte plusieurs réponses. Kenzo hoche la tête. On continue, avec papa. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11495,6 +11833,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11519,7 +11862,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Près de la voiture, Kenzo propose à Sami : le matin ? Sami dit : plus tard. Kenzo accepte plusieurs réponses. Papa reste tout près. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>Près de la voiture, Kenzo propose à Sami : le matin ? Plus tard. Kenzo accepte plusieurs réponses. Papa reste tout près. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -11657,6 +12000,13 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Près de la voiture, Kenzo propose à Sami : le matin ?
+enfant-m|Plus tard.
+narrateur|Kenzo accepte plusieurs réponses. Papa reste tout près. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12193,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12005,6 +12360,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi la voiture. Puis Tom. Puis le matin. Un panier est posé sur le banc. Kenzo sourit. Papa sourit aussi. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12527,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12329,6 +12694,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'arrête près de après la sieste. Tom est rangé. On écoute jusqu'au bout. Kenzo répète tout bas le geste. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12861,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12653,6 +13028,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo se souvient de la voiture. Et de Tom. Et de le soir. On rit un peu. Kenzo essuie ses mains. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13195,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12977,6 +13362,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Près de la voiture, Kenzo propose à Sami : après la sieste ? Sami dit oui. Kenzo propose, sans forcer. Papa montre le geste, lentement. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13553,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13325,6 +13720,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le matin. Après Léa. Près de la voiture. Kenzo s'arrête. Un ballon s'immobilise. Kenzo ferme le sac. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13887,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13649,6 +14054,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo range Léa. après la sieste reste près de la voiture. On entend un oiseau. Kenzo range la tasse. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14221,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13835,7 +14250,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>le soir est là. Léa aussi. la voiture reste dans le souvenir. On dit merci. Kenzo écoute papa encore une fois. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Le soir est là. Léa aussi. la voiture reste dans le souvenir. On dit merci. Kenzo écoute papa encore une fois. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13973,6 +14388,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir est là. Léa aussi. la voiture reste dans le souvenir. On dit merci. Kenzo écoute papa encore une fois. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14555,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14159,7 +14584,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Près de la voiture, Kenzo propose à Sami : le soir ? Sami dit non. Kenzo accepte plusieurs réponses. Papa dit : je suis là. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>Près de la voiture, Kenzo propose à Sami : le soir ? Sami dit non. Kenzo accepte plusieurs réponses. Je suis là. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14297,6 +14722,12 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Près de la voiture, Kenzo propose à Sami : le soir ? Sami dit non. Kenzo accepte plusieurs réponses.
+papa|Je suis là. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14914,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14645,6 +15081,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le matin. Sami est rangé. la voiture est fini. L'eau coule, tout petit bruit. Kenzo pose sa tête un moment. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15248,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14969,6 +15415,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Près de après la sieste. Kenzo pose Sami. la voiture est derrière. On se tient la main. Kenzo chuchote : c'est fini. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15582,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15293,6 +15749,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo montre le soir. Papa a vu la voiture. Et Sami. Une tasse cliquette. Kenzo marche près de papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15916,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15504,6 +15970,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-008.xlsx
+++ b/stories/arbres/TREE-DIF-008.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 papa|On propose. On peut accepter plusieurs réponses. On joue ensemble si l'autre veut. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1515,6 +1521,7 @@
           <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1683,6 +1690,7 @@
 papa|Plus tard, c'est possible. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1866,6 +1874,7 @@
           <t>narrateur|On propose sans forcer ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2037,6 +2046,7 @@
           <t>narrateur|Oui. On propose. On accepte plusieurs réponses. Kenzo respire. Papa est là. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2232,6 +2242,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2399,6 +2410,7 @@
           <t>narrateur|Près du train, Kenzo propose à Tom : on joue le matin ? Tom dit non. Kenzo accepte plusieurs réponses. Papa montre le geste, lentement. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2590,6 +2602,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2757,6 +2770,7 @@
           <t>narrateur|Kenzo a choisi le train. Puis Tom. Puis le matin. Le sol est un peu froid. Kenzo boit une gorgée d'eau. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2924,6 +2938,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3091,6 +3106,7 @@
           <t>narrateur|Kenzo s'arrête près de après la sieste. Tom est rangé. Un crochet tient bien le manteau. Kenzo montre après la sieste à papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3258,6 +3274,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3425,6 +3442,7 @@
           <t>narrateur|Kenzo se souvient de le train. Et de Tom. Et de le soir. Une chaussette est encore sablée. Kenzo pose Tom à sa place. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3592,6 +3610,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3762,6 +3781,7 @@
 papa|Je suis là. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3953,6 +3973,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4120,6 +4141,7 @@
           <t>narrateur|Avec le matin. Après Léa. Près de le train. Kenzo s'arrête. Il y a des miettes sur la table. Kenzo s'assoit près de papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4287,6 +4309,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4454,6 +4477,7 @@
           <t>narrateur|Kenzo range Léa. après la sieste reste près de le train. Un vélo passe au loin. Kenzo raccroche un linge. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4621,6 +4645,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4788,6 +4813,7 @@
           <t>narrateur|Le soir est là. Léa aussi. le train reste dans le souvenir. Ça sent le pain chaud. Kenzo range encore un peu, près de papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4955,6 +4981,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5124,6 +5151,7 @@
 narrateur|Kenzo accepte plusieurs réponses. Papa reste tout près. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5315,6 +5343,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5482,6 +5511,7 @@
           <t>narrateur|Kenzo rejoint le matin. Sami est rangé. le train est fini. On attend son tour. Kenzo tend le matin à maman. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5649,6 +5679,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5816,6 +5847,7 @@
           <t>narrateur|Près de après la sieste. Kenzo pose Sami. le train est derrière. Un ruban reste dans la poche. Kenzo caresse le doudou. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5983,6 +6015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6150,6 +6183,7 @@
           <t>narrateur|Kenzo montre le soir. Papa a vu le train. Et Sami. Les chaussures font toc toc. Kenzo ferme la porte, tout doux. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6317,6 +6351,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6486,6 +6521,7 @@
 narrateur|Kenzo accepte. On propose. On peut accepter plusieurs réponses. Maman tient le panier. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6669,6 +6705,7 @@
           <t>narrateur|On accepte plusieurs réponses ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6840,6 +6877,7 @@
           <t>narrateur|Oui. On propose. On accepte plusieurs réponses. Kenzo retient le geste. Papa sourit. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7035,6 +7073,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7203,6 +7242,7 @@
 papa|Je suis là. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7394,6 +7434,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7561,6 +7602,7 @@
           <t>narrateur|Kenzo a choisi le bus. Puis Tom. Puis le matin. On souffle doucement. Kenzo dit merci à papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7728,6 +7770,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7895,6 +7938,7 @@
           <t>narrateur|Kenzo s'arrête près de après la sieste. Tom est rangé. On range un objet. Kenzo serre la main de papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8062,6 +8106,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8229,6 +8274,7 @@
           <t>narrateur|Kenzo se souvient de le bus. Et de Tom. Et de le soir. Un chat miaule une fois. Kenzo prend la main de papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8396,6 +8442,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8563,6 +8610,7 @@
           <t>narrateur|Près du bus, Kenzo propose à Léa : après la sieste ? Léa dit non. Kenzo accepte plusieurs réponses. Papa reste tout près. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8754,6 +8802,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8921,6 +8970,7 @@
           <t>narrateur|Avec le matin. Après Léa. Près de le bus. Kenzo s'arrête. Un linge sèche à l'air. Kenzo enfile ses chaussons. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9088,6 +9138,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9255,6 +9306,7 @@
           <t>narrateur|Kenzo range Léa. après la sieste reste près de le bus. La couverture est douce. Kenzo souffle, puis sourit à papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9422,6 +9474,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9589,6 +9642,7 @@
           <t>narrateur|Le soir est là. Léa aussi. le bus reste dans le souvenir. Le vent est doux. Kenzo range le bus dans sa tête, comme un souvenir. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9756,6 +9810,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9925,6 +9980,7 @@
 narrateur|Kenzo accepte plusieurs réponses. Papa montre le geste, lentement. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10116,6 +10172,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10283,6 +10340,7 @@
           <t>narrateur|Kenzo rejoint le matin. Sami est rangé. le bus est fini. La lumière est claire. Maman n'est pas loin. Kenzo les rejoint. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10450,6 +10508,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10619,6 +10678,7 @@
 narrateur|Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10786,6 +10846,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10953,6 +11014,7 @@
           <t>narrateur|Kenzo montre le soir. Papa a vu le bus. Et Sami. Une cloche tinte, tout loin. Kenzo plie un pull. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11120,6 +11182,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11289,6 +11352,7 @@
 narrateur|Kenzo accepte. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11472,6 +11536,7 @@
           <t>narrateur|On invite, et après ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11643,6 +11708,7 @@
           <t>narrateur|Oui. On propose. On accepte plusieurs réponses. Kenzo hoche la tête. On continue, avec papa. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11838,6 +11904,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12007,6 +12074,7 @@
 narrateur|Kenzo accepte plusieurs réponses. Papa reste tout près. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12198,6 +12266,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12365,6 +12434,7 @@
           <t>narrateur|Kenzo a choisi la voiture. Puis Tom. Puis le matin. Un panier est posé sur le banc. Kenzo sourit. Papa sourit aussi. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12532,6 +12602,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12699,6 +12770,7 @@
           <t>narrateur|Kenzo s'arrête près de après la sieste. Tom est rangé. On écoute jusqu'au bout. Kenzo répète tout bas le geste. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12866,6 +12938,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13033,6 +13106,7 @@
           <t>narrateur|Kenzo se souvient de la voiture. Et de Tom. Et de le soir. On rit un peu. Kenzo essuie ses mains. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13200,6 +13274,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13367,6 +13442,7 @@
           <t>narrateur|Près de la voiture, Kenzo propose à Sami : après la sieste ? Sami dit oui. Kenzo propose, sans forcer. Papa montre le geste, lentement. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13558,6 +13634,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13725,6 +13802,7 @@
           <t>narrateur|Avec le matin. Après Léa. Près de la voiture. Kenzo s'arrête. Un ballon s'immobilise. Kenzo ferme le sac. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13892,6 +13970,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14059,6 +14138,7 @@
           <t>narrateur|Kenzo range Léa. après la sieste reste près de la voiture. On entend un oiseau. Kenzo range la tasse. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14226,6 +14306,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14393,6 +14474,7 @@
           <t>narrateur|Le soir est là. Léa aussi. la voiture reste dans le souvenir. On dit merci. Kenzo écoute papa encore une fois. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14560,6 +14642,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14728,6 +14811,7 @@
 papa|Je suis là. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14919,6 +15003,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15086,6 +15171,7 @@
           <t>narrateur|Kenzo rejoint le matin. Sami est rangé. la voiture est fini. L'eau coule, tout petit bruit. Kenzo pose sa tête un moment. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15253,6 +15339,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15420,6 +15507,7 @@
           <t>narrateur|Près de après la sieste. Kenzo pose Sami. la voiture est derrière. On se tient la main. Kenzo chuchote : c'est fini. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15587,6 +15675,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15754,6 +15843,7 @@
           <t>narrateur|Kenzo montre le soir. Papa a vu la voiture. Et Sami. Une tasse cliquette. Kenzo marche près de papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15921,6 +16011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15939,7 +16030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15977,6 +16068,20 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15991,7 +16096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16178,6 +16283,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-008.xlsx
+++ b/stories/arbres/TREE-DIF-008.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Inviter sans forcer — au marché</t>
+          <t>La goutte du store et le stand de Raphaël</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Au marché, une goutte tombe du store. Raphaël veut jouer avec Mila près des jouets en bois. Il propose. Mila dit non, je regarde, ou plus tard. Il accepte plusieurs réponses.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kenzo est au marché, avec papa. Maman tient le panier. Kenzo veut inviter un copain. Le copain peut dire non. On propose. On peut accepter plusieurs réponses. On joue ensemble si l'autre veut. On peut jouer ensemble.</t>
+          <t>Une caisse d'oranges tremble, tout bas. Une goutte glisse du store rayé. Elle fait ploc sur le pavé. Le pavé est encore mouillé, tout gris. Une feuille de chou colle à la chaussure de Raphaël. Le panier de maman a une anse rêche. Papa plie un sac en toile, un peu lourd. Ça sent la fraise écrasée, sur le papier. Une poule glousse, tout loin, derrière le stand. Mila a un manteau rouge, trop long. Les manches cachent un peu ses mains. Tu entends la poule, Raphaël ? Oui, papa. Les fraises sont froides. Le panier pique un peu. L'anse est en osier. En ce moment, Raphaël touche le bois du stand. Le bois est rêche, puis lisse. Un train en bois attend sur le stand. Un bus jaune est à côté. Une petite voiture verte brille. Mila regarde les roues, tout calme. On peut proposer un jeu, Raphaël. Oui, maman. Mila peut dire non. Ou regarder. Ou plus tard.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,11 +1337,40 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo est au marché, avec papa. Maman tient le panier. Kenzo veut inviter un copain. Le copain peut dire non.
-papa|On propose. On peut accepter plusieurs réponses. On joue ensemble si l'autre veut. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Une caisse d'oranges tremble, tout bas.
+narrateur|Une goutte glisse du store rayé.
+narrateur|Elle fait ploc sur le pavé.
+narrateur|Le pavé est encore mouillé, tout gris.
+narrateur|Une feuille de chou colle à la chaussure de Raphaël.
+narrateur|Le panier de maman a une anse rêche.
+narrateur|Papa plie un sac en toile, un peu lourd.
+narrateur|Ça sent la fraise écrasée, sur le papier.
+narrateur|Une poule glousse, tout loin, derrière le stand.
+narrateur|Mila a un manteau rouge, trop long.
+narrateur|Les manches cachent un peu ses mains.
+papa|Tu entends la poule, Raphaël ?
+enfant-m|Oui, papa.
+enfant-m|Les fraises sont froides.
+maman|Le panier pique un peu.
+maman|L'anse est en osier.
+narrateur|En ce moment, Raphaël touche le bois du stand.
+narrateur|Le bois est rêche, puis lisse.
+narrateur|Un train en bois attend sur le stand.
+narrateur|Un bus jaune est à côté.
+narrateur|Une petite voiture verte brille.
+narrateur|Mila regarde les roues, tout calme.
+maman|On peut proposer un jeu, Raphaël.
+enfant-m|Oui, maman.
+papa|Mila peut dire non.
+papa|Ou regarder.
+papa|Ou plus tard.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>goutte</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1354,7 +1395,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le train, le bus, ou la voiture.</t>
+          <t>Trois jouets en bois attendent. Le train, le bus, ou la voiture ? On propose. On accepte plusieurs réponses. On joue ensemble si l'autre veut.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1518,7 +1559,11 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
+          <t>narrateur|Trois jouets en bois attendent.
+papa|Le train, le bus, ou la voiture ?
+maman|On propose.
+maman|On accepte plusieurs réponses.
+papa|On joue ensemble si l'autre veut.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1546,7 +1591,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Kenzo voit le train du marché, un petit train en bois. Il propose à Tom : tu viens ? Tom dit non. Kenzo accepte. On propose. On peut accepter plusieurs réponses. Plus tard, c'est possible. On peut jouer ensemble.</t>
+          <t>Raphaël prend le train en bois. Les roues sont rouges, un peu rêches. Ça sent le pin, tout doux. Un wagon minuscule a une fenêtre peinte. Mila, tu viens ? Non. Raphaël garde le train dans ses mains. D'accord. Tu as proposé. On peut accepter plusieurs réponses. Non, c'est une réponse. Bravo, Raphaël. Tu as fait du bon travail. Plus tard, c'est possible. Le train reste sur la caisse, tout calme. Une orange roule, tout près.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1686,8 +1731,22 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo voit le train du marché, un petit train en bois. Il propose à Tom : tu viens ? Tom dit non. Kenzo accepte. On propose. On peut accepter plusieurs réponses.
-papa|Plus tard, c'est possible. On peut jouer ensemble.</t>
+          <t>narrateur|Raphaël prend le train en bois.
+narrateur|Les roues sont rouges, un peu rêches.
+narrateur|Ça sent le pin, tout doux.
+narrateur|Un wagon minuscule a une fenêtre peinte.
+enfant-m|Mila, tu viens ?
+copine|Non.
+narrateur|Raphaël garde le train dans ses mains.
+enfant-m|D'accord.
+papa|Tu as proposé.
+papa|On peut accepter plusieurs réponses.
+maman|Non, c'est une réponse.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Plus tard, c'est possible.
+narrateur|Le train reste sur la caisse, tout calme.
+narrateur|Une orange roule, tout près.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1715,7 +1774,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On propose sans forcer ?</t>
+          <t>Raphaël a proposé le train. On propose sans forcer ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1871,7 +1930,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|On propose sans forcer ?</t>
+          <t>narrateur|Raphaël a proposé le train.
+papa|On propose sans forcer ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1899,7 +1959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. On propose. On accepte plusieurs réponses. Kenzo respire. Papa est là. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>Oui. On propose. On accepte plusieurs réponses. Raphaël souffle un peu. Le bois du train reste froid. D'accord, Mila. Bravo. C'est du bon travail. Une goutte tombe encore du store.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2043,7 +2103,15 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On propose. On accepte plusieurs réponses. Kenzo respire. Papa est là. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>papa|Oui.
+papa|On propose.
+papa|On accepte plusieurs réponses.
+narrateur|Raphaël souffle un peu.
+narrateur|Le bois du train reste froid.
+enfant-m|D'accord, Mila.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Une goutte tombe encore du store.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2071,7 +2139,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches attendent sur le stand. Un ours, une poupée, un canard. Tom, Léa, ou Sami ? On propose. On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2239,7 +2307,11 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches attendent sur le stand.
+narrateur|Un ours, une poupée, un canard.
+maman|Tom, Léa, ou Sami ?
+papa|On propose.
+papa|On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2267,7 +2339,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Près du train, Kenzo propose à Tom : on joue le matin ? Tom dit non. Kenzo accepte plusieurs réponses. Papa montre le geste, lentement. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>Raphaël prend l'ours Tom. Le ventre a une tache de fraise. Une oreille est un peu froissée. Tu viens avec Tom ? Non. D'accord. Tu as proposé. On peut accepter plusieurs réponses. Bravo. L'ours Tom reste contre le panier. Une roue rouge touche l'oreille de Tom. On est encore près de le train en bois. On propose. On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2407,7 +2479,20 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Près du train, Kenzo propose à Tom : on joue le matin ? Tom dit non. Kenzo accepte plusieurs réponses. Papa montre le geste, lentement. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>narrateur|Raphaël prend l'ours Tom.
+narrateur|Le ventre a une tache de fraise.
+narrateur|Une oreille est un peu froissée.
+enfant-m|Tu viens avec Tom ?
+copine|Non.
+enfant-m|D'accord.
+papa|Tu as proposé.
+maman|On peut accepter plusieurs réponses.
+papa|Bravo.
+narrateur|L'ours Tom reste contre le panier.
+narrateur|Une roue rouge touche l'oreille de Tom.
+narrateur|On est encore près de le train en bois.
+maman|On propose.
+maman|On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2435,7 +2520,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On propose encore. On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2599,7 +2684,10 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On propose encore.
+maman|On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2627,7 +2715,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi le train. Puis Tom. Puis le matin. Le sol est un peu froid. Kenzo boit une gorgée d'eau. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Le matin, le soleil pose sur les oranges. Une goutte brille encore, sur le store. Ça sent le cacao, au stand du pain. Bonjour, Raphaël. Bonjour, papa. Raphaël a encore le train en bois. Il tient l'ours Tom. L'ours Tom a du soleil sur le museau. Mila, tu viens ? Non. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2767,10 +2855,32 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi le train. Puis Tom. Puis le matin. Le sol est un peu froid. Kenzo boit une gorgée d'eau. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|Le matin, le soleil pose sur les oranges.
+narrateur|Une goutte brille encore, sur le store.
+narrateur|Ça sent le cacao, au stand du pain.
+papa|Bonjour, Raphaël.
+enfant-m|Bonjour, papa.
+narrateur|Raphaël a encore le train en bois.
+narrateur|Il tient l'ours Tom.
+narrateur|L'ours Tom a du soleil sur le museau.
+enfant-m|Mila, tu viens ?
+copine|Non.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range l'ours Tom, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2795,7 +2905,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu le matin, près du stand. Il a joué avec le train en bois. Il a tenu l'ours Tom. Une orange garde encore le soleil. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2935,7 +3045,15 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu le matin, près du stand.
+narrateur|Il a joué avec le train en bois.
+narrateur|Il a tenu l'ours Tom.
+narrateur|Une orange garde encore le soleil.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2963,7 +3081,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Kenzo s'arrête près de après la sieste. Tom est rangé. Un crochet tient bien le manteau. Kenzo montre après la sieste à papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Après la sieste, les pavés sont chauds. Le panier a un pli, tout doux. La place est plus calme, un peu. Tu es réveillé ? Oui, maman. Raphaël a encore le train en bois. Il tient l'ours Tom. L'ours Tom chauffe contre le wagon. Mila, tu viens ? Non. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3103,7 +3221,25 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo s'arrête près de après la sieste. Tom est rangé. Un crochet tient bien le manteau. Kenzo montre après la sieste à papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>narrateur|Après la sieste, les pavés sont chauds.
+narrateur|Le panier a un pli, tout doux.
+narrateur|La place est plus calme, un peu.
+maman|Tu es réveillé ?
+enfant-m|Oui, maman.
+narrateur|Raphaël a encore le train en bois.
+narrateur|Il tient l'ours Tom.
+narrateur|L'ours Tom chauffe contre le wagon.
+enfant-m|Mila, tu viens ?
+copine|Non.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3131,7 +3267,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu après la sieste, près du stand. Il a joué avec le train en bois. Il a tenu l'ours Tom. Le pavé redevient calme, tout chaud. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3271,7 +3407,15 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu après la sieste, près du stand.
+narrateur|Il a joué avec le train en bois.
+narrateur|Il a tenu l'ours Tom.
+narrateur|Le pavé redevient calme, tout chaud.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3299,7 +3443,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Kenzo se souvient de le train. Et de Tom. Et de le soir. Une chaussette est encore sablée. Kenzo pose Tom à sa place. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Le soir, une lanterne fait un rond. Ça sent le pain, tout chaud. Les caisses claquent, tout loin. Te voilà, Raphaël. Bonjour, papa. Raphaël a encore le train en bois. Il tient l'ours Tom. L'ours Tom a une ombre de lanterne. Mila, tu viens ? Non. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3439,10 +3583,32 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo se souvient de le train. Et de Tom. Et de le soir. Une chaussette est encore sablée. Kenzo pose Tom à sa place. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|Le soir, une lanterne fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les caisses claquent, tout loin.
+papa|Te voilà, Raphaël.
+enfant-m|Bonjour, papa.
+narrateur|Raphaël a encore le train en bois.
+narrateur|Il tient l'ours Tom.
+narrateur|L'ours Tom a une ombre de lanterne.
+enfant-m|Mila, tu viens ?
+copine|Non.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range l'ours Tom, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3467,7 +3633,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu le soir, près du stand. Il a joué avec le train en bois. Il a tenu l'ours Tom. La lanterne reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3607,7 +3773,15 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu le soir, près du stand.
+narrateur|Il a joué avec le train en bois.
+narrateur|Il a tenu l'ours Tom.
+narrateur|La lanterne reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3635,7 +3809,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Près du train, Kenzo propose à Tom : après la sieste ? Je regarde. Kenzo accepte plusieurs réponses. Je suis là. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>Raphaël prend la poupée Léa. Elle a un chapeau de paille, tout petit. Un bouton brille, tout rond. Tu joues avec Léa ? Je regarde. D'accord. Regarder, c'est une réponse. On peut proposer. On accepte plusieurs réponses. La poupée Léa s'assoit près des oranges. La poupée Léa a le chapeau dans le wagon. On est encore près de le train en bois. On propose. On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3775,10 +3949,20 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Près du train, Kenzo propose à Tom : après la sieste ?
-enfant-m|Je regarde.
-narrateur|Kenzo accepte plusieurs réponses.
-papa|Je suis là. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>narrateur|Raphaël prend la poupée Léa.
+narrateur|Elle a un chapeau de paille, tout petit.
+narrateur|Un bouton brille, tout rond.
+enfant-m|Tu joues avec Léa ?
+copine|Je regarde.
+enfant-m|D'accord.
+maman|Regarder, c'est une réponse.
+papa|On peut proposer.
+papa|On accepte plusieurs réponses.
+narrateur|La poupée Léa s'assoit près des oranges.
+narrateur|La poupée Léa a le chapeau dans le wagon.
+narrateur|On est encore près de le train en bois.
+maman|On propose.
+maman|On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3806,7 +3990,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On propose encore. On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3970,7 +4154,10 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On propose encore.
+maman|On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -3998,7 +4185,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Avec le matin. Après Léa. Près de le train. Kenzo s'arrête. Il y a des miettes sur la table. Kenzo s'assoit près de papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Le matin, le soleil pose sur les oranges. Une goutte brille encore, sur le store. Ça sent le cacao, au stand du pain. Bonjour, Raphaël. Bonjour, papa. Raphaël a encore le train en bois. Il tient la poupée Léa. La poupée Léa a le chapeau tout clair. Mila, tu viens ? Je regarde. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4138,10 +4325,32 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Avec le matin. Après Léa. Près de le train. Kenzo s'arrête. Il y a des miettes sur la table. Kenzo s'assoit près de papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|Le matin, le soleil pose sur les oranges.
+narrateur|Une goutte brille encore, sur le store.
+narrateur|Ça sent le cacao, au stand du pain.
+papa|Bonjour, Raphaël.
+enfant-m|Bonjour, papa.
+narrateur|Raphaël a encore le train en bois.
+narrateur|Il tient la poupée Léa.
+narrateur|La poupée Léa a le chapeau tout clair.
+enfant-m|Mila, tu viens ?
+copine|Je regarde.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range la poupée Léa, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4166,7 +4375,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu le matin, près du stand. Il a joué avec le train en bois. Il a tenu la poupée Léa. Une orange garde encore le soleil. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4306,7 +4515,15 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu le matin, près du stand.
+narrateur|Il a joué avec le train en bois.
+narrateur|Il a tenu la poupée Léa.
+narrateur|Une orange garde encore le soleil.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4334,7 +4551,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Kenzo range Léa. après la sieste reste près de le train. Un vélo passe au loin. Kenzo raccroche un linge. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Après la sieste, les pavés sont chauds. Le panier a un pli, tout doux. La place est plus calme, un peu. Tu es réveillé ? Oui, maman. Raphaël a encore le train en bois. Il tient la poupée Léa. La poupée Léa s'adosse au train, tout calme. Mila, tu viens ? Je regarde. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4474,7 +4691,25 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo range Léa. après la sieste reste près de le train. Un vélo passe au loin. Kenzo raccroche un linge. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>narrateur|Après la sieste, les pavés sont chauds.
+narrateur|Le panier a un pli, tout doux.
+narrateur|La place est plus calme, un peu.
+maman|Tu es réveillé ?
+enfant-m|Oui, maman.
+narrateur|Raphaël a encore le train en bois.
+narrateur|Il tient la poupée Léa.
+narrateur|La poupée Léa s'adosse au train, tout calme.
+enfant-m|Mila, tu viens ?
+copine|Je regarde.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4502,7 +4737,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu après la sieste, près du stand. Il a joué avec le train en bois. Il a tenu la poupée Léa. Le pavé redevient calme, tout chaud. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4642,7 +4877,15 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu après la sieste, près du stand.
+narrateur|Il a joué avec le train en bois.
+narrateur|Il a tenu la poupée Léa.
+narrateur|Le pavé redevient calme, tout chaud.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4670,7 +4913,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Le soir est là. Léa aussi. le train reste dans le souvenir. Ça sent le pain chaud. Kenzo range encore un peu, près de papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Le soir, une lanterne fait un rond. Ça sent le pain, tout chaud. Les caisses claquent, tout loin. Te voilà, Raphaël. Bonjour, papa. Raphaël a encore le train en bois. Il tient la poupée Léa. La poupée Léa brille sous la lanterne. Mila, tu viens ? Je regarde. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4810,10 +5053,32 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Le soir est là. Léa aussi. le train reste dans le souvenir. Ça sent le pain chaud. Kenzo range encore un peu, près de papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|Le soir, une lanterne fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les caisses claquent, tout loin.
+papa|Te voilà, Raphaël.
+enfant-m|Bonjour, papa.
+narrateur|Raphaël a encore le train en bois.
+narrateur|Il tient la poupée Léa.
+narrateur|La poupée Léa brille sous la lanterne.
+enfant-m|Mila, tu viens ?
+copine|Je regarde.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range la poupée Léa, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4838,7 +5103,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu le soir, près du stand. Il a joué avec le train en bois. Il a tenu la poupée Léa. La lanterne reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4978,7 +5243,15 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu le soir, près du stand.
+narrateur|Il a joué avec le train en bois.
+narrateur|Il a tenu la poupée Léa.
+narrateur|La lanterne reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5006,7 +5279,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Près du train, Kenzo propose à Tom : le soir ? Plus tard. Kenzo accepte plusieurs réponses. Papa reste tout près. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>Raphaël prend le canard Sami. Le bec est en bois, tout lisse. Le jaune a une poussière de marché. Plus tard, avec Sami ? Plus tard. D'accord. Plus tard, c'est possible. On peut accepter plusieurs réponses. Le canard Sami penche la tête. Le canard Sami penche vers le train. On est encore près de le train en bois. On propose. On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5146,9 +5419,19 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Près du train, Kenzo propose à Tom : le soir ?
-enfant-m|Plus tard.
-narrateur|Kenzo accepte plusieurs réponses. Papa reste tout près. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>narrateur|Raphaël prend le canard Sami.
+narrateur|Le bec est en bois, tout lisse.
+narrateur|Le jaune a une poussière de marché.
+enfant-m|Plus tard, avec Sami ?
+copine|Plus tard.
+enfant-m|D'accord.
+papa|Plus tard, c'est possible.
+maman|On peut accepter plusieurs réponses.
+narrateur|Le canard Sami penche la tête.
+narrateur|Le canard Sami penche vers le train.
+narrateur|On est encore près de le train en bois.
+maman|On propose.
+maman|On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5176,7 +5459,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On propose encore. On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5340,7 +5623,10 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On propose encore.
+maman|On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5368,7 +5654,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le matin. Sami est rangé. le train est fini. On attend son tour. Kenzo tend le matin à maman. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Le matin, le soleil pose sur les oranges. Une goutte brille encore, sur le store. Ça sent le cacao, au stand du pain. Bonjour, Raphaël. Bonjour, papa. Raphaël a encore le train en bois. Il tient le canard Sami. Le canard Sami a une goutte sur le bec. Mila, tu viens ? Plus tard. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range le canard Sami, tout doux.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5508,10 +5794,32 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint le matin. Sami est rangé. le train est fini. On attend son tour. Kenzo tend le matin à maman. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|Le matin, le soleil pose sur les oranges.
+narrateur|Une goutte brille encore, sur le store.
+narrateur|Ça sent le cacao, au stand du pain.
+papa|Bonjour, Raphaël.
+enfant-m|Bonjour, papa.
+narrateur|Raphaël a encore le train en bois.
+narrateur|Il tient le canard Sami.
+narrateur|Le canard Sami a une goutte sur le bec.
+enfant-m|Mila, tu viens ?
+copine|Plus tard.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range le canard Sami, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5536,7 +5844,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu le matin, près du stand. Il a joué avec le train en bois. Il a tenu le canard Sami. Une orange garde encore le soleil. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5676,7 +5984,15 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu le matin, près du stand.
+narrateur|Il a joué avec le train en bois.
+narrateur|Il a tenu le canard Sami.
+narrateur|Une orange garde encore le soleil.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5704,7 +6020,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Près de après la sieste. Kenzo pose Sami. le train est derrière. Un ruban reste dans la poche. Kenzo caresse le doudou. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Après la sieste, les pavés sont chauds. Le panier a un pli, tout doux. La place est plus calme, un peu. Tu es réveillé ? Oui, maman. Raphaël a encore le train en bois. Il tient le canard Sami. Le canard Sami est tiède, près du wagon. Mila, tu viens ? Plus tard. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range le canard Sami, tout doux.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5844,7 +6160,25 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Près de après la sieste. Kenzo pose Sami. le train est derrière. Un ruban reste dans la poche. Kenzo caresse le doudou. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>narrateur|Après la sieste, les pavés sont chauds.
+narrateur|Le panier a un pli, tout doux.
+narrateur|La place est plus calme, un peu.
+maman|Tu es réveillé ?
+enfant-m|Oui, maman.
+narrateur|Raphaël a encore le train en bois.
+narrateur|Il tient le canard Sami.
+narrateur|Le canard Sami est tiède, près du wagon.
+enfant-m|Mila, tu viens ?
+copine|Plus tard.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range le canard Sami, tout doux.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5872,7 +6206,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu après la sieste, près du stand. Il a joué avec le train en bois. Il a tenu le canard Sami. Le pavé redevient calme, tout chaud. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6012,7 +6346,15 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu après la sieste, près du stand.
+narrateur|Il a joué avec le train en bois.
+narrateur|Il a tenu le canard Sami.
+narrateur|Le pavé redevient calme, tout chaud.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6040,7 +6382,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Kenzo montre le soir. Papa a vu le train. Et Sami. Les chaussures font toc toc. Kenzo ferme la porte, tout doux. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Le soir, une lanterne fait un rond. Ça sent le pain, tout chaud. Les caisses claquent, tout loin. Te voilà, Raphaël. Bonjour, papa. Raphaël a encore le train en bois. Il tient le canard Sami. Le canard Sami écoute les caisses, tout loin. Mila, tu viens ? Plus tard. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range le canard Sami, tout doux.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6180,10 +6522,32 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo montre le soir. Papa a vu le train. Et Sami. Les chaussures font toc toc. Kenzo ferme la porte, tout doux. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|Le soir, une lanterne fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les caisses claquent, tout loin.
+papa|Te voilà, Raphaël.
+enfant-m|Bonjour, papa.
+narrateur|Raphaël a encore le train en bois.
+narrateur|Il tient le canard Sami.
+narrateur|Le canard Sami écoute les caisses, tout loin.
+enfant-m|Mila, tu viens ?
+copine|Plus tard.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range le canard Sami, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6208,7 +6572,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu le soir, près du stand. Il a joué avec le train en bois. Il a tenu le canard Sami. La lanterne reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6348,7 +6712,15 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu le soir, près du stand.
+narrateur|Il a joué avec le train en bois.
+narrateur|Il a tenu le canard Sami.
+narrateur|La lanterne reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6376,7 +6748,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Kenzo voit le bus s'arrêter. Il propose à Léa : tu viens voir ? Je regarde. Kenzo accepte. On propose. On peut accepter plusieurs réponses. Maman tient le panier. On peut jouer ensemble.</t>
+          <t>Raphaël pousse le bus jaune. Les fenêtres sont peintes en bleu. Une roue fait un petit clic. Le pavé est froid sous les genoux. Tu viens voir le bus ? Je regarde. Mila reste près du panier. D'accord. Regarder, c'est une réponse. On peut proposer. On peut accepter plusieurs réponses. Bravo, Raphaël. Tu as su attendre. Le bus s'arrête près d'une fraise. Le papier tache un peu le jaune.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6516,9 +6888,21 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo voit le bus s'arrêter. Il propose à Léa : tu viens voir ?
-enfant-f|Je regarde.
-narrateur|Kenzo accepte. On propose. On peut accepter plusieurs réponses. Maman tient le panier. On peut jouer ensemble.</t>
+          <t>narrateur|Raphaël pousse le bus jaune.
+narrateur|Les fenêtres sont peintes en bleu.
+narrateur|Une roue fait un petit clic.
+narrateur|Le pavé est froid sous les genoux.
+enfant-m|Tu viens voir le bus ?
+copine|Je regarde.
+narrateur|Mila reste près du panier.
+enfant-m|D'accord.
+maman|Regarder, c'est une réponse.
+papa|On peut proposer.
+papa|On peut accepter plusieurs réponses.
+maman|Bravo, Raphaël.
+papa|Tu as su attendre.
+narrateur|Le bus s'arrête près d'une fraise.
+narrateur|Le papier tache un peu le jaune.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6546,7 +6930,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>On accepte plusieurs réponses ?</t>
+          <t>Mila regarde le bus. On accepte plusieurs réponses ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6702,7 +7086,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|On accepte plusieurs réponses ?</t>
+          <t>narrateur|Mila regarde le bus.
+maman|On accepte plusieurs réponses ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6730,7 +7115,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. On propose. On accepte plusieurs réponses. Kenzo retient le geste. Papa sourit. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>Oui. On propose. On accepte plusieurs réponses. Raphaël laisse une place, tout près. Tu regardes. Bravo. C'est du bon travail. Le bus jaune reste immobile.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6874,7 +7259,14 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On propose. On accepte plusieurs réponses. Kenzo retient le geste. Papa sourit. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>maman|Oui.
+maman|On propose.
+maman|On accepte plusieurs réponses.
+narrateur|Raphaël laisse une place, tout près.
+enfant-m|Tu regardes.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Le bus jaune reste immobile.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6902,7 +7294,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches attendent sur le stand. Un ours, une poupée, un canard. Tom, Léa, ou Sami ? On propose. On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7070,7 +7462,11 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches attendent sur le stand.
+narrateur|Un ours, une poupée, un canard.
+maman|Tom, Léa, ou Sami ?
+papa|On propose.
+papa|On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7098,7 +7494,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Près du bus, Kenzo propose à Léa : le matin ? Léa dit oui. Kenzo propose, sans forcer. Je suis là. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>Raphaël prend l'ours Tom. Le ventre a une tache de fraise. Une oreille est un peu froissée. Tu viens avec Tom ? Non. D'accord. Tu as proposé. On peut accepter plusieurs réponses. Bravo. L'ours Tom reste contre le panier. L'ours Tom a le museau contre le bus. On est encore près de le bus jaune. On propose. On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7238,8 +7634,20 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Près du bus, Kenzo propose à Léa : le matin ? Léa dit oui. Kenzo propose, sans forcer.
-papa|Je suis là. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>narrateur|Raphaël prend l'ours Tom.
+narrateur|Le ventre a une tache de fraise.
+narrateur|Une oreille est un peu froissée.
+enfant-m|Tu viens avec Tom ?
+copine|Non.
+enfant-m|D'accord.
+papa|Tu as proposé.
+maman|On peut accepter plusieurs réponses.
+papa|Bravo.
+narrateur|L'ours Tom reste contre le panier.
+narrateur|L'ours Tom a le museau contre le bus.
+narrateur|On est encore près de le bus jaune.
+maman|On propose.
+maman|On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7267,7 +7675,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On propose encore. On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7431,7 +7839,10 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On propose encore.
+maman|On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7459,7 +7870,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi le bus. Puis Tom. Puis le matin. On souffle doucement. Kenzo dit merci à papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Le matin, le soleil pose sur les oranges. Une goutte brille encore, sur le store. Ça sent le cacao, au stand du pain. Bonjour, Raphaël. Bonjour, papa. Raphaël a encore le bus jaune. Il tient l'ours Tom. L'ours Tom regarde le bus jaune, tout calme. Mila, tu viens ? Non. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7599,10 +8010,32 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi le bus. Puis Tom. Puis le matin. On souffle doucement. Kenzo dit merci à papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|Le matin, le soleil pose sur les oranges.
+narrateur|Une goutte brille encore, sur le store.
+narrateur|Ça sent le cacao, au stand du pain.
+papa|Bonjour, Raphaël.
+enfant-m|Bonjour, papa.
+narrateur|Raphaël a encore le bus jaune.
+narrateur|Il tient l'ours Tom.
+narrateur|L'ours Tom regarde le bus jaune, tout calme.
+enfant-m|Mila, tu viens ?
+copine|Non.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range l'ours Tom, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7627,7 +8060,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu le matin, près du stand. Il a joué avec le bus jaune. Il a tenu l'ours Tom. Une orange garde encore le soleil. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7767,7 +8200,15 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu le matin, près du stand.
+narrateur|Il a joué avec le bus jaune.
+narrateur|Il a tenu l'ours Tom.
+narrateur|Une orange garde encore le soleil.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7795,7 +8236,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Kenzo s'arrête près de après la sieste. Tom est rangé. On range un objet. Kenzo serre la main de papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Après la sieste, les pavés sont chauds. Le panier a un pli, tout doux. La place est plus calme, un peu. Tu es réveillé ? Oui, maman. Raphaël a encore le bus jaune. Il tient l'ours Tom. L'ours Tom a une poussière de pavé. Mila, tu viens ? Non. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7935,7 +8376,25 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo s'arrête près de après la sieste. Tom est rangé. On range un objet. Kenzo serre la main de papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>narrateur|Après la sieste, les pavés sont chauds.
+narrateur|Le panier a un pli, tout doux.
+narrateur|La place est plus calme, un peu.
+maman|Tu es réveillé ?
+enfant-m|Oui, maman.
+narrateur|Raphaël a encore le bus jaune.
+narrateur|Il tient l'ours Tom.
+narrateur|L'ours Tom a une poussière de pavé.
+enfant-m|Mila, tu viens ?
+copine|Non.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7963,7 +8422,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu après la sieste, près du stand. Il a joué avec le bus jaune. Il a tenu l'ours Tom. Le pavé redevient calme, tout chaud. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8103,7 +8562,15 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu après la sieste, près du stand.
+narrateur|Il a joué avec le bus jaune.
+narrateur|Il a tenu l'ours Tom.
+narrateur|Le pavé redevient calme, tout chaud.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8131,7 +8598,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Kenzo se souvient de le bus. Et de Tom. Et de le soir. Un chat miaule une fois. Kenzo prend la main de papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Le soir, une lanterne fait un rond. Ça sent le pain, tout chaud. Les caisses claquent, tout loin. Te voilà, Raphaël. Bonjour, papa. Raphaël a encore le bus jaune. Il tient l'ours Tom. L'ours Tom penche vers le bus, tout doux. Mila, tu viens ? Non. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8271,10 +8738,32 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo se souvient de le bus. Et de Tom. Et de le soir. Un chat miaule une fois. Kenzo prend la main de papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|Le soir, une lanterne fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les caisses claquent, tout loin.
+papa|Te voilà, Raphaël.
+enfant-m|Bonjour, papa.
+narrateur|Raphaël a encore le bus jaune.
+narrateur|Il tient l'ours Tom.
+narrateur|L'ours Tom penche vers le bus, tout doux.
+enfant-m|Mila, tu viens ?
+copine|Non.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range l'ours Tom, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8299,7 +8788,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu le soir, près du stand. Il a joué avec le bus jaune. Il a tenu l'ours Tom. La lanterne reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8439,7 +8928,15 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu le soir, près du stand.
+narrateur|Il a joué avec le bus jaune.
+narrateur|Il a tenu l'ours Tom.
+narrateur|La lanterne reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8467,7 +8964,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Près du bus, Kenzo propose à Léa : après la sieste ? Léa dit non. Kenzo accepte plusieurs réponses. Papa reste tout près. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>Raphaël prend la poupée Léa. Elle a un chapeau de paille, tout petit. Un bouton brille, tout rond. Tu joues avec Léa ? Je regarde. D'accord. Regarder, c'est une réponse. On peut proposer. On accepte plusieurs réponses. La poupée Léa s'assoit près des oranges. La poupée Léa regarde une fenêtre peinte. On est encore près de le bus jaune. On propose. On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8607,7 +9104,20 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Près du bus, Kenzo propose à Léa : après la sieste ? Léa dit non. Kenzo accepte plusieurs réponses. Papa reste tout près. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>narrateur|Raphaël prend la poupée Léa.
+narrateur|Elle a un chapeau de paille, tout petit.
+narrateur|Un bouton brille, tout rond.
+enfant-m|Tu joues avec Léa ?
+copine|Je regarde.
+enfant-m|D'accord.
+maman|Regarder, c'est une réponse.
+papa|On peut proposer.
+papa|On accepte plusieurs réponses.
+narrateur|La poupée Léa s'assoit près des oranges.
+narrateur|La poupée Léa regarde une fenêtre peinte.
+narrateur|On est encore près de le bus jaune.
+maman|On propose.
+maman|On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8635,7 +9145,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On propose encore. On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8799,7 +9309,10 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On propose encore.
+maman|On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8827,7 +9340,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Avec le matin. Après Léa. Près de le bus. Kenzo s'arrête. Un linge sèche à l'air. Kenzo enfile ses chaussons. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Le matin, le soleil pose sur les oranges. Une goutte brille encore, sur le store. Ça sent le cacao, au stand du pain. Bonjour, Raphaël. Bonjour, papa. Raphaël a encore le bus jaune. Il tient la poupée Léa. La poupée Léa a le chapeau contre le bus. Mila, tu viens ? Je regarde. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8967,10 +9480,32 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Avec le matin. Après Léa. Près de le bus. Kenzo s'arrête. Un linge sèche à l'air. Kenzo enfile ses chaussons. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|Le matin, le soleil pose sur les oranges.
+narrateur|Une goutte brille encore, sur le store.
+narrateur|Ça sent le cacao, au stand du pain.
+papa|Bonjour, Raphaël.
+enfant-m|Bonjour, papa.
+narrateur|Raphaël a encore le bus jaune.
+narrateur|Il tient la poupée Léa.
+narrateur|La poupée Léa a le chapeau contre le bus.
+enfant-m|Mila, tu viens ?
+copine|Je regarde.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range la poupée Léa, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8995,7 +9530,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu le matin, près du stand. Il a joué avec le bus jaune. Il a tenu la poupée Léa. Une orange garde encore le soleil. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9135,7 +9670,15 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu le matin, près du stand.
+narrateur|Il a joué avec le bus jaune.
+narrateur|Il a tenu la poupée Léa.
+narrateur|Une orange garde encore le soleil.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9163,7 +9706,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Kenzo range Léa. après la sieste reste près de le bus. La couverture est douce. Kenzo souffle, puis sourit à papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Après la sieste, les pavés sont chauds. Le panier a un pli, tout doux. La place est plus calme, un peu. Tu es réveillé ? Oui, maman. Raphaël a encore le bus jaune. Il tient la poupée Léa. La poupée Léa a chaud, près du pavé. Mila, tu viens ? Je regarde. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9303,7 +9846,25 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo range Léa. après la sieste reste près de le bus. La couverture est douce. Kenzo souffle, puis sourit à papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>narrateur|Après la sieste, les pavés sont chauds.
+narrateur|Le panier a un pli, tout doux.
+narrateur|La place est plus calme, un peu.
+maman|Tu es réveillé ?
+enfant-m|Oui, maman.
+narrateur|Raphaël a encore le bus jaune.
+narrateur|Il tient la poupée Léa.
+narrateur|La poupée Léa a chaud, près du pavé.
+enfant-m|Mila, tu viens ?
+copine|Je regarde.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9331,7 +9892,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu après la sieste, près du stand. Il a joué avec le bus jaune. Il a tenu la poupée Léa. Le pavé redevient calme, tout chaud. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9471,7 +10032,15 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu après la sieste, près du stand.
+narrateur|Il a joué avec le bus jaune.
+narrateur|Il a tenu la poupée Léa.
+narrateur|Le pavé redevient calme, tout chaud.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9499,7 +10068,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Le soir est là. Léa aussi. le bus reste dans le souvenir. Le vent est doux. Kenzo range le bus dans sa tête, comme un souvenir. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Le soir, une lanterne fait un rond. Ça sent le pain, tout chaud. Les caisses claquent, tout loin. Te voilà, Raphaël. Bonjour, papa. Raphaël a encore le bus jaune. Il tient la poupée Léa. La poupée Léa a une ombre de roue. Mila, tu viens ? Je regarde. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9639,10 +10208,32 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Le soir est là. Léa aussi. le bus reste dans le souvenir. Le vent est doux. Kenzo range le bus dans sa tête, comme un souvenir. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|Le soir, une lanterne fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les caisses claquent, tout loin.
+papa|Te voilà, Raphaël.
+enfant-m|Bonjour, papa.
+narrateur|Raphaël a encore le bus jaune.
+narrateur|Il tient la poupée Léa.
+narrateur|La poupée Léa a une ombre de roue.
+enfant-m|Mila, tu viens ?
+copine|Je regarde.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range la poupée Léa, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9667,7 +10258,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu le soir, près du stand. Il a joué avec le bus jaune. Il a tenu la poupée Léa. La lanterne reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9807,7 +10398,15 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu le soir, près du stand.
+narrateur|Il a joué avec le bus jaune.
+narrateur|Il a tenu la poupée Léa.
+narrateur|La lanterne reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9835,7 +10434,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Près du bus, Kenzo propose à Léa : le soir ? Je regarde. Kenzo accepte plusieurs réponses. Papa montre le geste, lentement. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>Raphaël prend le canard Sami. Le bec est en bois, tout lisse. Le jaune a une poussière de marché. Plus tard, avec Sami ? Plus tard. D'accord. Plus tard, c'est possible. On peut accepter plusieurs réponses. Le canard Sami penche la tête. Le canard Sami a une poussière jaune. On est encore près de le bus jaune. On propose. On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9975,9 +10574,19 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Près du bus, Kenzo propose à Léa : le soir ?
-enfant-f|Je regarde.
-narrateur|Kenzo accepte plusieurs réponses. Papa montre le geste, lentement. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>narrateur|Raphaël prend le canard Sami.
+narrateur|Le bec est en bois, tout lisse.
+narrateur|Le jaune a une poussière de marché.
+enfant-m|Plus tard, avec Sami ?
+copine|Plus tard.
+enfant-m|D'accord.
+papa|Plus tard, c'est possible.
+maman|On peut accepter plusieurs réponses.
+narrateur|Le canard Sami penche la tête.
+narrateur|Le canard Sami a une poussière jaune.
+narrateur|On est encore près de le bus jaune.
+maman|On propose.
+maman|On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -10005,7 +10614,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On propose encore. On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10169,7 +10778,10 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On propose encore.
+maman|On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10197,7 +10809,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le matin. Sami est rangé. le bus est fini. La lumière est claire. Maman n'est pas loin. Kenzo les rejoint. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Le matin, le soleil pose sur les oranges. Une goutte brille encore, sur le store. Ça sent le cacao, au stand du pain. Bonjour, Raphaël. Bonjour, papa. Raphaël a encore le bus jaune. Il tient le canard Sami. Le canard Sami glisse près d'une roue jaune. Mila, tu viens ? Plus tard. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range le canard Sami, tout doux.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10337,10 +10949,32 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint le matin. Sami est rangé. le bus est fini. La lumière est claire. Maman n'est pas loin. Kenzo les rejoint. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|Le matin, le soleil pose sur les oranges.
+narrateur|Une goutte brille encore, sur le store.
+narrateur|Ça sent le cacao, au stand du pain.
+papa|Bonjour, Raphaël.
+enfant-m|Bonjour, papa.
+narrateur|Raphaël a encore le bus jaune.
+narrateur|Il tient le canard Sami.
+narrateur|Le canard Sami glisse près d'une roue jaune.
+enfant-m|Mila, tu viens ?
+copine|Plus tard.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range le canard Sami, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10365,7 +10999,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu le matin, près du stand. Il a joué avec le bus jaune. Il a tenu le canard Sami. Une orange garde encore le soleil. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10505,7 +11139,15 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu le matin, près du stand.
+narrateur|Il a joué avec le bus jaune.
+narrateur|Il a tenu le canard Sami.
+narrateur|Une orange garde encore le soleil.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10533,7 +11175,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Près de après la sieste. Kenzo pose Sami. le bus est derrière. Un galet est encore chaud. J'ai appris. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Après la sieste, les pavés sont chauds. Le panier a un pli, tout doux. La place est plus calme, un peu. Tu es réveillé ? Oui, maman. Raphaël a encore le bus jaune. Il tient le canard Sami. Le canard Sami a le bec sur le bus. Mila, tu viens ? Plus tard. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range le canard Sami, tout doux.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10673,9 +11315,25 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Près de après la sieste. Kenzo pose Sami. le bus est derrière. Un galet est encore chaud.
-enfant-m|J'ai appris. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard.
-narrateur|Kenzo dit merci à papa.</t>
+          <t>narrateur|Après la sieste, les pavés sont chauds.
+narrateur|Le panier a un pli, tout doux.
+narrateur|La place est plus calme, un peu.
+maman|Tu es réveillé ?
+enfant-m|Oui, maman.
+narrateur|Raphaël a encore le bus jaune.
+narrateur|Il tient le canard Sami.
+narrateur|Le canard Sami a le bec sur le bus.
+enfant-m|Mila, tu viens ?
+copine|Plus tard.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range le canard Sami, tout doux.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10703,7 +11361,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu après la sieste, près du stand. Il a joué avec le bus jaune. Il a tenu le canard Sami. Le pavé redevient calme, tout chaud. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10843,7 +11501,15 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu après la sieste, près du stand.
+narrateur|Il a joué avec le bus jaune.
+narrateur|Il a tenu le canard Sami.
+narrateur|Le pavé redevient calme, tout chaud.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10871,7 +11537,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Kenzo montre le soir. Papa a vu le bus. Et Sami. Une cloche tinte, tout loin. Kenzo plie un pull. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Le soir, une lanterne fait un rond. Ça sent le pain, tout chaud. Les caisses claquent, tout loin. Te voilà, Raphaël. Bonjour, papa. Raphaël a encore le bus jaune. Il tient le canard Sami. Le canard Sami écoute un clic, tout petit. Mila, tu viens ? Plus tard. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range le canard Sami, tout doux.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11011,10 +11677,32 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo montre le soir. Papa a vu le bus. Et Sami. Une cloche tinte, tout loin. Kenzo plie un pull. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|Le soir, une lanterne fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les caisses claquent, tout loin.
+papa|Te voilà, Raphaël.
+enfant-m|Bonjour, papa.
+narrateur|Raphaël a encore le bus jaune.
+narrateur|Il tient le canard Sami.
+narrateur|Le canard Sami écoute un clic, tout petit.
+enfant-m|Mila, tu viens ?
+copine|Plus tard.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range le canard Sami, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11039,7 +11727,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu le soir, près du stand. Il a joué avec le bus jaune. Il a tenu le canard Sami. La lanterne reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11179,7 +11867,15 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu le soir, près du stand.
+narrateur|Il a joué avec le bus jaune.
+narrateur|Il a tenu le canard Sami.
+narrateur|La lanterne reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11207,7 +11903,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Kenzo s'approche de la voiture de courses, un jouet. Il propose à Sami : on joue ? Plus tard. Kenzo accepte. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>Raphaël prend la petite voiture verte. Le capot est lisse, un peu froid. Une portière peinte a un point blanc. Ça sent encore la fraise, tout près. On joue ? Plus tard. D'accord. Plus tard, c'est une réponse. On peut proposer. On peut accepter plusieurs réponses. Bravo, Raphaël. Tu as accepté. La voiture verte attend sur le stand. Une feuille de chou tremble au vent.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11347,9 +12043,20 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo s'approche de la voiture de courses, un jouet. Il propose à Sami : on joue ?
-enfant-m|Plus tard.
-narrateur|Kenzo accepte. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>narrateur|Raphaël prend la petite voiture verte.
+narrateur|Le capot est lisse, un peu froid.
+narrateur|Une portière peinte a un point blanc.
+narrateur|Ça sent encore la fraise, tout près.
+enfant-m|On joue ?
+copine|Plus tard.
+enfant-m|D'accord.
+papa|Plus tard, c'est une réponse.
+maman|On peut proposer.
+maman|On peut accepter plusieurs réponses.
+papa|Bravo, Raphaël.
+maman|Tu as accepté.
+narrateur|La voiture verte attend sur le stand.
+narrateur|Une feuille de chou tremble au vent.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11377,7 +12084,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>On invite, et après ?</t>
+          <t>Raphaël a invité Mila. On invite, et après ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11533,7 +12240,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|On invite, et après ?</t>
+          <t>narrateur|Raphaël a invité Mila.
+papa|On invite, et après ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11561,7 +12269,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. On propose. On accepte plusieurs réponses. Kenzo hoche la tête. On continue, avec papa. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>Oui. On propose. On accepte plusieurs réponses. Raphaël hoche la tête. Plus tard, d'accord. Bravo. Tu as fait du bon travail. Le sac de papa penche un peu.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11705,7 +12413,14 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On propose. On accepte plusieurs réponses. Kenzo hoche la tête. On continue, avec papa. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>papa|Oui.
+papa|On propose.
+papa|On accepte plusieurs réponses.
+narrateur|Raphaël hoche la tête.
+enfant-m|Plus tard, d'accord.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le sac de papa penche un peu.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11733,7 +12448,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches attendent sur le stand. Un ours, une poupée, un canard. Tom, Léa, ou Sami ? On propose. On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11901,7 +12616,11 @@
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches attendent sur le stand.
+narrateur|Un ours, une poupée, un canard.
+maman|Tom, Léa, ou Sami ?
+papa|On propose.
+papa|On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11929,7 +12648,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Près de la voiture, Kenzo propose à Sami : le matin ? Plus tard. Kenzo accepte plusieurs réponses. Papa reste tout près. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>Raphaël prend l'ours Tom. Le ventre a une tache de fraise. Une oreille est un peu froissée. Tu viens avec Tom ? Non. D'accord. Tu as proposé. On peut accepter plusieurs réponses. Bravo. L'ours Tom reste contre le panier. L'ours Tom est trop grand pour la voiture. On est encore près de la voiture verte. On propose. On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12069,9 +12788,20 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Près de la voiture, Kenzo propose à Sami : le matin ?
-enfant-m|Plus tard.
-narrateur|Kenzo accepte plusieurs réponses. Papa reste tout près. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>narrateur|Raphaël prend l'ours Tom.
+narrateur|Le ventre a une tache de fraise.
+narrateur|Une oreille est un peu froissée.
+enfant-m|Tu viens avec Tom ?
+copine|Non.
+enfant-m|D'accord.
+papa|Tu as proposé.
+maman|On peut accepter plusieurs réponses.
+papa|Bravo.
+narrateur|L'ours Tom reste contre le panier.
+narrateur|L'ours Tom est trop grand pour la voiture.
+narrateur|On est encore près de la voiture verte.
+maman|On propose.
+maman|On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12099,7 +12829,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On propose encore. On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12263,7 +12993,10 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On propose encore.
+maman|On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12291,7 +13024,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi la voiture. Puis Tom. Puis le matin. Un panier est posé sur le banc. Kenzo sourit. Papa sourit aussi. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Le matin, le soleil pose sur les oranges. Une goutte brille encore, sur le store. Ça sent le cacao, au stand du pain. Bonjour, Raphaël. Bonjour, papa. Raphaël a encore la voiture verte. Il tient l'ours Tom. L'ours Tom tient le capot vert, trop grand. Mila, tu viens ? Non. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12431,10 +13164,32 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi la voiture. Puis Tom. Puis le matin. Un panier est posé sur le banc. Kenzo sourit. Papa sourit aussi. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|Le matin, le soleil pose sur les oranges.
+narrateur|Une goutte brille encore, sur le store.
+narrateur|Ça sent le cacao, au stand du pain.
+papa|Bonjour, Raphaël.
+enfant-m|Bonjour, papa.
+narrateur|Raphaël a encore la voiture verte.
+narrateur|Il tient l'ours Tom.
+narrateur|L'ours Tom tient le capot vert, trop grand.
+enfant-m|Mila, tu viens ?
+copine|Non.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range l'ours Tom, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12459,7 +13214,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu le matin, près du stand. Il a joué avec la voiture verte. Il a tenu l'ours Tom. Une orange garde encore le soleil. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12599,7 +13354,15 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu le matin, près du stand.
+narrateur|Il a joué avec la voiture verte.
+narrateur|Il a tenu l'ours Tom.
+narrateur|Une orange garde encore le soleil.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12627,7 +13390,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Kenzo s'arrête près de après la sieste. Tom est rangé. On écoute jusqu'au bout. Kenzo répète tout bas le geste. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Après la sieste, les pavés sont chauds. Le panier a un pli, tout doux. La place est plus calme, un peu. Tu es réveillé ? Oui, maman. Raphaël a encore la voiture verte. Il tient l'ours Tom. L'ours Tom a le ventre tiède, près de la voiture. Mila, tu viens ? Non. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12767,7 +13530,25 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo s'arrête près de après la sieste. Tom est rangé. On écoute jusqu'au bout. Kenzo répète tout bas le geste. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>narrateur|Après la sieste, les pavés sont chauds.
+narrateur|Le panier a un pli, tout doux.
+narrateur|La place est plus calme, un peu.
+maman|Tu es réveillé ?
+enfant-m|Oui, maman.
+narrateur|Raphaël a encore la voiture verte.
+narrateur|Il tient l'ours Tom.
+narrateur|L'ours Tom a le ventre tiède, près de la voiture.
+enfant-m|Mila, tu viens ?
+copine|Non.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12795,7 +13576,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu après la sieste, près du stand. Il a joué avec la voiture verte. Il a tenu l'ours Tom. Le pavé redevient calme, tout chaud. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12935,7 +13716,15 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu après la sieste, près du stand.
+narrateur|Il a joué avec la voiture verte.
+narrateur|Il a tenu l'ours Tom.
+narrateur|Le pavé redevient calme, tout chaud.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12963,7 +13752,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Kenzo se souvient de la voiture. Et de Tom. Et de le soir. On rit un peu. Kenzo essuie ses mains. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Le soir, une lanterne fait un rond. Ça sent le pain, tout chaud. Les caisses claquent, tout loin. Te voilà, Raphaël. Bonjour, papa. Raphaël a encore la voiture verte. Il tient l'ours Tom. L'ours Tom a une ombre verte, tout longue. Mila, tu viens ? Non. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13103,10 +13892,32 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo se souvient de la voiture. Et de Tom. Et de le soir. On rit un peu. Kenzo essuie ses mains. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|Le soir, une lanterne fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les caisses claquent, tout loin.
+papa|Te voilà, Raphaël.
+enfant-m|Bonjour, papa.
+narrateur|Raphaël a encore la voiture verte.
+narrateur|Il tient l'ours Tom.
+narrateur|L'ours Tom a une ombre verte, tout longue.
+enfant-m|Mila, tu viens ?
+copine|Non.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range l'ours Tom, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13131,7 +13942,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu le soir, près du stand. Il a joué avec la voiture verte. Il a tenu l'ours Tom. La lanterne reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13271,7 +14082,15 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu le soir, près du stand.
+narrateur|Il a joué avec la voiture verte.
+narrateur|Il a tenu l'ours Tom.
+narrateur|La lanterne reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13299,7 +14118,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Près de la voiture, Kenzo propose à Sami : après la sieste ? Sami dit oui. Kenzo propose, sans forcer. Papa montre le geste, lentement. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>Raphaël prend la poupée Léa. Elle a un chapeau de paille, tout petit. Un bouton brille, tout rond. Tu joues avec Léa ? Je regarde. D'accord. Regarder, c'est une réponse. On peut proposer. On accepte plusieurs réponses. La poupée Léa s'assoit près des oranges. La poupée Léa a le chapeau sur le capot. On est encore près de la voiture verte. On propose. On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13439,7 +14258,20 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Près de la voiture, Kenzo propose à Sami : après la sieste ? Sami dit oui. Kenzo propose, sans forcer. Papa montre le geste, lentement. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>narrateur|Raphaël prend la poupée Léa.
+narrateur|Elle a un chapeau de paille, tout petit.
+narrateur|Un bouton brille, tout rond.
+enfant-m|Tu joues avec Léa ?
+copine|Je regarde.
+enfant-m|D'accord.
+maman|Regarder, c'est une réponse.
+papa|On peut proposer.
+papa|On accepte plusieurs réponses.
+narrateur|La poupée Léa s'assoit près des oranges.
+narrateur|La poupée Léa a le chapeau sur le capot.
+narrateur|On est encore près de la voiture verte.
+maman|On propose.
+maman|On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13467,7 +14299,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On propose encore. On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13631,7 +14463,10 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On propose encore.
+maman|On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13659,7 +14494,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Avec le matin. Après Léa. Près de la voiture. Kenzo s'arrête. Un ballon s'immobilise. Kenzo ferme le sac. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Le matin, le soleil pose sur les oranges. Une goutte brille encore, sur le store. Ça sent le cacao, au stand du pain. Bonjour, Raphaël. Bonjour, papa. Raphaël a encore la voiture verte. Il tient la poupée Léa. La poupée Léa a le bouton contre le capot. Mila, tu viens ? Je regarde. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13799,10 +14634,32 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Avec le matin. Après Léa. Près de la voiture. Kenzo s'arrête. Un ballon s'immobilise. Kenzo ferme le sac. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|Le matin, le soleil pose sur les oranges.
+narrateur|Une goutte brille encore, sur le store.
+narrateur|Ça sent le cacao, au stand du pain.
+papa|Bonjour, Raphaël.
+enfant-m|Bonjour, papa.
+narrateur|Raphaël a encore la voiture verte.
+narrateur|Il tient la poupée Léa.
+narrateur|La poupée Léa a le bouton contre le capot.
+enfant-m|Mila, tu viens ?
+copine|Je regarde.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range la poupée Léa, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13827,7 +14684,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu le matin, près du stand. Il a joué avec la voiture verte. Il a tenu la poupée Léa. Une orange garde encore le soleil. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13967,7 +14824,15 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu le matin, près du stand.
+narrateur|Il a joué avec la voiture verte.
+narrateur|Il a tenu la poupée Léa.
+narrateur|Une orange garde encore le soleil.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -13995,7 +14860,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Kenzo range Léa. après la sieste reste près de la voiture. On entend un oiseau. Kenzo range la tasse. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Après la sieste, les pavés sont chauds. Le panier a un pli, tout doux. La place est plus calme, un peu. Tu es réveillé ? Oui, maman. Raphaël a encore la voiture verte. Il tient la poupée Léa. La poupée Léa s'assoit près de la portière. Mila, tu viens ? Je regarde. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14135,7 +15000,25 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo range Léa. après la sieste reste près de la voiture. On entend un oiseau. Kenzo range la tasse. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>narrateur|Après la sieste, les pavés sont chauds.
+narrateur|Le panier a un pli, tout doux.
+narrateur|La place est plus calme, un peu.
+maman|Tu es réveillé ?
+enfant-m|Oui, maman.
+narrateur|Raphaël a encore la voiture verte.
+narrateur|Il tient la poupée Léa.
+narrateur|La poupée Léa s'assoit près de la portière.
+enfant-m|Mila, tu viens ?
+copine|Je regarde.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14163,7 +15046,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu après la sieste, près du stand. Il a joué avec la voiture verte. Il a tenu la poupée Léa. Le pavé redevient calme, tout chaud. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14303,7 +15186,15 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu après la sieste, près du stand.
+narrateur|Il a joué avec la voiture verte.
+narrateur|Il a tenu la poupée Léa.
+narrateur|Le pavé redevient calme, tout chaud.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14331,7 +15222,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Le soir est là. Léa aussi. la voiture reste dans le souvenir. On dit merci. Kenzo écoute papa encore une fois. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Le soir, une lanterne fait un rond. Ça sent le pain, tout chaud. Les caisses claquent, tout loin. Te voilà, Raphaël. Bonjour, papa. Raphaël a encore la voiture verte. Il tient la poupée Léa. La poupée Léa brille, près du point blanc. Mila, tu viens ? Je regarde. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14471,10 +15362,32 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Le soir est là. Léa aussi. la voiture reste dans le souvenir. On dit merci. Kenzo écoute papa encore une fois. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|Le soir, une lanterne fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les caisses claquent, tout loin.
+papa|Te voilà, Raphaël.
+enfant-m|Bonjour, papa.
+narrateur|Raphaël a encore la voiture verte.
+narrateur|Il tient la poupée Léa.
+narrateur|La poupée Léa brille, près du point blanc.
+enfant-m|Mila, tu viens ?
+copine|Je regarde.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range la poupée Léa, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14499,7 +15412,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu le soir, près du stand. Il a joué avec la voiture verte. Il a tenu la poupée Léa. La lanterne reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14639,7 +15552,15 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu le soir, près du stand.
+narrateur|Il a joué avec la voiture verte.
+narrateur|Il a tenu la poupée Léa.
+narrateur|La lanterne reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14667,7 +15588,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Près de la voiture, Kenzo propose à Sami : le soir ? Sami dit non. Kenzo accepte plusieurs réponses. Je suis là. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>Raphaël prend le canard Sami. Le bec est en bois, tout lisse. Le jaune a une poussière de marché. Plus tard, avec Sami ? Plus tard. D'accord. Plus tard, c'est possible. On peut accepter plusieurs réponses. Le canard Sami penche la tête. Le canard Sami glisse près de la portière. On est encore près de la voiture verte. On propose. On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14807,8 +15728,19 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Près de la voiture, Kenzo propose à Sami : le soir ? Sami dit non. Kenzo accepte plusieurs réponses.
-papa|Je suis là. On propose. On peut accepter plusieurs réponses. On peut jouer ensemble.</t>
+          <t>narrateur|Raphaël prend le canard Sami.
+narrateur|Le bec est en bois, tout lisse.
+narrateur|Le jaune a une poussière de marché.
+enfant-m|Plus tard, avec Sami ?
+copine|Plus tard.
+enfant-m|D'accord.
+papa|Plus tard, c'est possible.
+maman|On peut accepter plusieurs réponses.
+narrateur|Le canard Sami penche la tête.
+narrateur|Le canard Sami glisse près de la portière.
+narrateur|On est encore près de la voiture verte.
+maman|On propose.
+maman|On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14836,7 +15768,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On propose encore. On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15000,7 +15932,10 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On propose encore.
+maman|On accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15028,7 +15963,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le matin. Sami est rangé. la voiture est fini. L'eau coule, tout petit bruit. Kenzo pose sa tête un moment. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Le matin, le soleil pose sur les oranges. Une goutte brille encore, sur le store. Ça sent le cacao, au stand du pain. Bonjour, Raphaël. Bonjour, papa. Raphaël a encore la voiture verte. Il tient le canard Sami. Le canard Sami a le bec sur le capot. Mila, tu viens ? Plus tard. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range le canard Sami, tout doux.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15168,10 +16103,32 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint le matin. Sami est rangé. la voiture est fini. L'eau coule, tout petit bruit. Kenzo pose sa tête un moment. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|Le matin, le soleil pose sur les oranges.
+narrateur|Une goutte brille encore, sur le store.
+narrateur|Ça sent le cacao, au stand du pain.
+papa|Bonjour, Raphaël.
+enfant-m|Bonjour, papa.
+narrateur|Raphaël a encore la voiture verte.
+narrateur|Il tient le canard Sami.
+narrateur|Le canard Sami a le bec sur le capot.
+enfant-m|Mila, tu viens ?
+copine|Plus tard.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range le canard Sami, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15196,7 +16153,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu le matin, près du stand. Il a joué avec la voiture verte. Il a tenu le canard Sami. Une orange garde encore le soleil. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15336,7 +16293,15 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu le matin, près du stand.
+narrateur|Il a joué avec la voiture verte.
+narrateur|Il a tenu le canard Sami.
+narrateur|Une orange garde encore le soleil.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15364,7 +16329,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Près de après la sieste. Kenzo pose Sami. la voiture est derrière. On se tient la main. Kenzo chuchote : c'est fini. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Après la sieste, les pavés sont chauds. Le panier a un pli, tout doux. La place est plus calme, un peu. Tu es réveillé ? Oui, maman. Raphaël a encore la voiture verte. Il tient le canard Sami. Le canard Sami est tiède, comme le pavé. Mila, tu viens ? Plus tard. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range le canard Sami, tout doux.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15504,7 +16469,25 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Près de après la sieste. Kenzo pose Sami. la voiture est derrière. On se tient la main. Kenzo chuchote : c'est fini. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>narrateur|Après la sieste, les pavés sont chauds.
+narrateur|Le panier a un pli, tout doux.
+narrateur|La place est plus calme, un peu.
+maman|Tu es réveillé ?
+enfant-m|Oui, maman.
+narrateur|Raphaël a encore la voiture verte.
+narrateur|Il tient le canard Sami.
+narrateur|Le canard Sami est tiède, comme le pavé.
+enfant-m|Mila, tu viens ?
+copine|Plus tard.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range le canard Sami, tout doux.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15532,7 +16515,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu après la sieste, près du stand. Il a joué avec la voiture verte. Il a tenu le canard Sami. Le pavé redevient calme, tout chaud. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15672,7 +16655,15 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu après la sieste, près du stand.
+narrateur|Il a joué avec la voiture verte.
+narrateur|Il a tenu le canard Sami.
+narrateur|Le pavé redevient calme, tout chaud.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15700,7 +16691,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Kenzo montre le soir. Papa a vu la voiture. Et Sami. Une tasse cliquette. Kenzo marche près de papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
+          <t>Le soir, une lanterne fait un rond. Ça sent le pain, tout chaud. Les caisses claquent, tout loin. Te voilà, Raphaël. Bonjour, papa. Raphaël a encore la voiture verte. Il tient le canard Sami. Le canard Sami écoute la lanterne, tout bas. Mila, tu viens ? Plus tard. D'accord. On propose. On accepte plusieurs réponses. Non, regarder, ou plus tard. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. Merci, maman. Raphaël range le canard Sami, tout doux.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15840,10 +16831,32 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo montre le soir. Papa a vu la voiture. Et Sami. Une tasse cliquette. Kenzo marche près de papa. On propose. On peut accepter plusieurs réponses. On invite. On accepte non, regarder, ou plus tard. Kenzo dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|Le soir, une lanterne fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les caisses claquent, tout loin.
+papa|Te voilà, Raphaël.
+enfant-m|Bonjour, papa.
+narrateur|Raphaël a encore la voiture verte.
+narrateur|Il tient le canard Sami.
+narrateur|Le canard Sami écoute la lanterne, tout bas.
+enfant-m|Mila, tu viens ?
+copine|Plus tard.
+enfant-m|D'accord.
+papa|On propose.
+maman|On accepte plusieurs réponses.
+maman|Non, regarder, ou plus tard.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Raphaël range le canard Sami, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15868,7 +16881,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo, Raphaël. Tu as fait du bon travail. Raphaël a vécu le soir, près du stand. Il a joué avec la voiture verte. Il a tenu le canard Sami. La lanterne reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16008,7 +17021,15 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé.
+enfant-m|J'ai accepté.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël a vécu le soir, près du stand.
+narrateur|Il a joué avec la voiture verte.
+narrateur|Il a tenu le canard Sami.
+narrateur|La lanterne reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16030,7 +17051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16082,6 +17103,13 @@
       <c r="A7" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-008.xlsx
+++ b/stories/arbres/TREE-DIF-008.xlsx
@@ -1197,17 +1197,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La goutte grossit au bord de la toile. Elle tremble, puis choisit le bois de l'étal. Un grain de cannelle s'y colle, brun et minuscule. Le marché assemble ses caisses, sans crier. Ça sent l'écorce mouillée, et le fruit coupé. Tu as vu ce grain, Raphaël ? Il est coincé dans l'eau. La toile va goutter longtemps. Une caisse glisse sur le bois mouillé. Raphaël la rattrape des deux mains. Merci, tu as tenu la caisse. Je tiens le stand, moi. Un fruit, pour Mila, tout de suite. En ce moment, Raphaël avance le bras vers elle. Mila arrive, les mains au fond des poches. Viens, c'est pour toi ! Mila ne dit rien. Ses doigts restent cachés. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et la peur se bousculent. Papa s'accroupit, à la hauteur des deux. Tu l'as vue, ses poches ? Elle n'a rien dit. Ses mains sont restées dedans.</t>
+          <t>La goutte grossit au bord de la toile. Elle tremble, puis choisit le bois de l'étal. Un grain de cannelle s'y colle, brun et minuscule. Il pique un peu, collé au bois mouillé. Le marché assemble ses caisses, sans crier. Des voix s'installent, plus loin, pas ici. Ça sent l'écorce mouillée, et le fruit coupé. Tu as vu ce grain, Raphaël ? Il est coincé dans l'eau. La toile va goutter longtemps. Une caisse glisse sur le bois mouillé. Raphaël la rattrape des deux mains. Merci, tu as tenu la caisse. Je tiens le stand, moi. Un fruit, pour Mila, tout de suite. En ce moment, Raphaël avance le bras vers elle. Mila arrive, les mains au fond des poches. Viens, c'est pour toi ! Mila ne dit rien. Ses doigts restent cachés. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et la peur se bousculent. Papa s'accroupit, à la hauteur des deux. Tu l'as vue, ses poches ? Elle n'a rien dit. Ses mains sont restées dedans.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La goutte grossit au bord de la toile. Elle tremble, puis choisit le bois de l'étal. Un &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; s'y colle, brun et minuscule. Le marché assemble ses caisses, sans crier. Ça sent l'écorce mouillée, et le fruit coupé. Tu as vu ce grain, Raphaël ? Il est coincé dans l'eau. La toile va goutter longtemps. Une caisse glisse sur le bois mouillé. Raphaël la rattrape des deux mains. Merci, tu as tenu la caisse. Je tiens le stand, moi. Un fruit, pour Mila, tout de suite. En ce moment, Raphaël avance le bras vers elle. Mila arrive, les mains au fond des poches. Viens, c'est pour toi ! Mila ne dit rien. Ses doigts restent cachés. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et la peur se bousculent. Papa s'accroupit, à la hauteur des deux. Tu l'as vue, ses poches ? Elle n'a rien dit. Ses mains sont restées dedans.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La goutte grossit au bord de la toile. Elle tremble, puis choisit le bois de l'étal. Un &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; s'y colle, brun et minuscule. Il pique un peu, collé au bois mouillé. Le marché assemble ses caisses, sans crier. Des voix s'installent, plus loin, pas ici. Ça sent l'écorce mouillée, et le fruit coupé. Tu as vu ce grain, Raphaël ? Il est coincé dans l'eau. La toile va goutter longtemps. Une caisse glisse sur le bois mouillé. Raphaël la rattrape des deux mains. Merci, tu as tenu la caisse. Je tiens le stand, moi. Un fruit, pour Mila, tout de suite. En ce moment, Raphaël avance le bras vers elle. Mila arrive, les mains au fond des poches. Viens, c'est pour toi ! Mila ne dit rien. Ses doigts restent cachés. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et la peur se bousculent. Papa s'accroupit, à la hauteur des deux. Tu l'as vue, ses poches ? Elle n'a rien dit. Ses mains sont restées dedans.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>La goutte grossit au bord de la toile. Elle tremble, puis choisit le bois de l'étal. Un &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; s'y colle, brun et minuscule. Le marché assemble ses caisses, sans crier. Ça sent l'écorce mouillée, et le fruit coupé. Tu as vu ce grain, Raphaël ? Il est coincé dans l'eau. La toile va goutter longtemps. Une caisse glisse sur le bois mouillé. Raphaël la rattrape des deux mains. Merci, tu as tenu la caisse. Je tiens le stand, moi. Un fruit, pour Mila, tout de suite. En ce moment, Raphaël avance le bras vers elle. Mila arrive, les mains au fond des poches. Viens, c'est pour toi ! Mila ne dit rien. Ses doigts restent cachés. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et la peur se bousculent. Papa s'accroupit, à la hauteur des deux. Tu l'as vue, ses poches ? Elle n'a rien dit. Ses mains sont restées dedans. [pause]</t>
+          <t>La goutte grossit au bord de la toile. Elle tremble, puis choisit le bois de l'étal. Un &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; s'y colle, brun et minuscule. Il pique un peu, collé au bois mouillé. Le marché assemble ses caisses, sans crier. Des voix s'installent, plus loin, pas ici. Ça sent l'écorce mouillée, et le fruit coupé. Tu as vu ce grain, Raphaël ? Il est coincé dans l'eau. La toile va goutter longtemps. Une caisse glisse sur le bois mouillé. Raphaël la rattrape des deux mains. Merci, tu as tenu la caisse. Je tiens le stand, moi. Un fruit, pour Mila, tout de suite. En ce moment, Raphaël avance le bras vers elle. Mila arrive, les mains au fond des poches. Viens, c'est pour toi ! Mila ne dit rien. Ses doigts restent cachés. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et la peur se bousculent. Papa s'accroupit, à la hauteur des deux. Tu l'as vue, ses poches ? Elle n'a rien dit. Ses mains sont restées dedans. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1344,7 +1344,9 @@
           <t>narrateur|La goutte grossit au bord de la toile.
 narrateur|Elle tremble, puis choisit le bois de l'étal.
 narrateur|Un grain de cannelle s'y colle, brun et minuscule.
+narrateur|Il pique un peu, collé au bois mouillé.
 narrateur|Le marché assemble ses caisses, sans crier.
+narrateur|Des voix s'installent, plus loin, pas ici.
 narrateur|Ça sent l'écorce mouillée, et le fruit coupé.
 papa|Tu as vu ce grain, Raphaël ?
 enfant-m|Il est coincé dans l'eau.
@@ -1598,17 +1600,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël glisse sous le store jaune. La toile jette des ronds d'or sur les citrons. Ils sentent le zeste, fort. La balance, le sac et la caisse restent là. Il cueille un citron, trop vite. Prends, Mila ! Mila recule d'un pas. Le citron reste seul, dans sa paume. Le sourire de Raphaël se plie. Elle n'a pas tendu les doigts. Maman s'accroupit, près des caisses jaunes. Une goutte dorée tremble au bord de la toile. Elle tombe près du grain de cannelle. Le grain est mouillé. Tu le vois, sur le bois ?</t>
+          <t>Raphaël glisse sous le store jaune. La toile jette des ronds d'or sur les citrons. Ils sentent le zeste, fort. La balance, le sac et la caisse restent là. Il cueille un citron, trop vite. Prends, Mila ! Mila recule d'un pas. Le citron reste seul, dans sa paume. Le sourire de Raphaël se plie. Elle n'a pas tendu les doigts. Maman s'accroupit, près des caisses jaunes. Une goutte dorée tremble au bord de la toile. Elle tombe près du grain de cannelle. Le grain est mouillé. Tu le vois, sur le bois ? Un client passe, sans s'arrêter.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Raphaël glisse sous le &lt;emphasis level="moderate"&gt;store jaune&lt;/emphasis&gt;. La toile jette des ronds d'or sur les citrons. Ils sentent le zeste, fort. La balance, le sac et la caisse restent là. Il cueille un citron, trop vite. Prends, Mila ! Mila recule d'un pas. Le citron reste seul, dans sa paume. Le sourire de Raphaël se plie. Elle n'a pas tendu les doigts. Maman s'accroupit, près des caisses jaunes. Une goutte dorée tremble au bord de la toile. Elle tombe près du grain de cannelle. Le grain est mouillé. Tu le vois, sur le bois ?&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Raphaël glisse sous le &lt;emphasis level="moderate"&gt;store jaune&lt;/emphasis&gt;. La toile jette des ronds d'or sur les citrons. Ils sentent le zeste, fort. La balance, le sac et la caisse restent là. Il cueille un citron, trop vite. Prends, Mila ! Mila recule d'un pas. Le citron reste seul, dans sa paume. Le sourire de Raphaël se plie. Elle n'a pas tendu les doigts. Maman s'accroupit, près des caisses jaunes. Une goutte dorée tremble au bord de la toile. Elle tombe près du grain de cannelle. Le grain est mouillé. Tu le vois, sur le bois ? Un client passe, sans s'arrêter.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël glisse sous le &lt;emphasis&gt;store jaune&lt;/emphasis&gt;. La toile jette des ronds d'or sur les citrons. Ils sentent le zeste, fort. La balance, le sac et la caisse restent là. Il cueille un citron, trop vite. Prends, Mila ! Mila recule d'un pas. Le citron reste seul, dans sa paume. Le sourire de Raphaël se plie. Elle n'a pas tendu les doigts. Maman s'accroupit, près des caisses jaunes. Une goutte dorée tremble au bord de la toile. Elle tombe près du grain de cannelle. Le grain est mouillé. Tu le vois, sur le bois ? [pause]</t>
+          <t>Raphaël glisse sous le &lt;emphasis&gt;store jaune&lt;/emphasis&gt;. La toile jette des ronds d'or sur les citrons. Ils sentent le zeste, fort. La balance, le sac et la caisse restent là. Il cueille un citron, trop vite. Prends, Mila ! Mila recule d'un pas. Le citron reste seul, dans sa paume. Le sourire de Raphaël se plie. Elle n'a pas tendu les doigts. Maman s'accroupit, près des caisses jaunes. Une goutte dorée tremble au bord de la toile. Elle tombe près du grain de cannelle. Le grain est mouillé. Tu le vois, sur le bois ? Un client passe, sans s'arrêter. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1756,7 +1758,8 @@
 narrateur|Une goutte dorée tremble au bord de la toile.
 narrateur|Elle tombe près du grain de cannelle.
 enfant-m|Le grain est mouillé.
-papa|Tu le vois, sur le bois ?</t>
+papa|Tu le vois, sur le bois ?
+narrateur|Un client passe, sans s'arrêter.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -2928,17 +2931,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Le stand a failli rester sans regard. Mila est restée au bord, les yeux ouverts. Tu as regardé le chiffre. Oui. L'aiguille ne danse plus. Le citron a gardé sa place. La goutte jaune a séché en croissant mince. Le grain de cannelle tient sur le plateau froid.</t>
+          <t>Le stand a failli rester sans regard. Mila est restée au bord, les yeux ouverts. Tu as regardé le chiffre. Oui. L'aiguille ne danse plus. Le citron a gardé sa place. La goutte jaune a séché en trait d'or. Le grain de cannelle tient sur le plateau froid.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le stand a failli rester sans regard. Mila est restée au bord, les yeux ouverts. Tu as regardé le chiffre. Oui. L'aiguille ne danse plus. Le citron a gardé sa place. La goutte jaune a séché en croissant mince. Le &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; tient sur le plateau froid.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le stand a failli rester sans regard. Mila est restée au bord, les yeux ouverts. Tu as regardé le chiffre. Oui. L'aiguille ne danse plus. Le citron a gardé sa place. La goutte jaune a séché en trait d'or. Le &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; tient sur le plateau froid.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le stand a failli rester sans regard. Mila est restée au bord, les yeux ouverts. Tu as regardé le chiffre. Oui. L'aiguille ne danse plus. Le citron a gardé sa place. La goutte jaune a séché en croissant mince. Le &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; tient sur le plateau froid.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le stand a failli rester sans regard. Mila est restée au bord, les yeux ouverts. Tu as regardé le chiffre. Oui. L'aiguille ne danse plus. Le citron a gardé sa place. La goutte jaune a séché en trait d'or. Le &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; tient sur le plateau froid.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -3082,7 +3085,7 @@
 enfant-f|Oui.
 papa|L'aiguille ne danse plus.
 maman|Le citron a gardé sa place.
-narrateur|La goutte jaune a séché en croissant mince.
+narrateur|La goutte jaune a séché en trait d'or.
 narrateur|Le grain de cannelle tient sur le plateau froid.</t>
         </is>
       </c>
@@ -3298,17 +3301,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Mila revient, les joues un peu chaudes. Maintenant ? Oui. C'est pour toi. Elle s'approche de la balance. Vous avez pris le temps. La goutte jaune n'est plus qu'un trait. Le citron attend, et le grain brille à côté.</t>
+          <t>Mila revient, les joues un peu chaudes. Maintenant ? Oui. C'est pour toi. Elle s'approche de la balance. Vous avez pris le temps. La goutte jaune n'est plus qu'un trait. Le citron attend, et le grain de cannelle brille à côté.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Mila revient, les joues un peu chaudes. Maintenant ? Oui. C'est pour toi. Elle s'approche de la balance. Vous avez pris le temps. La goutte jaune n'est plus qu'un trait. Le citron attend, et le grain brille à côté.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Mila revient, les joues un peu chaudes. Maintenant ? Oui. C'est pour toi. Elle s'approche de la balance. Vous avez pris le temps. La goutte jaune n'est plus qu'un trait. Le citron attend, et le &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; brille à côté.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Mila revient, les joues un peu chaudes. Maintenant ? Oui. C'est pour toi. Elle s'approche de la balance. Vous avez pris le temps. La goutte jaune n'est plus qu'un trait. Le citron attend, et le grain brille à côté.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Mila revient, les joues un peu chaudes. Maintenant ? Oui. C'est pour toi. Elle s'approche de la balance. Vous avez pris le temps. La goutte jaune n'est plus qu'un trait. Le citron attend, et le &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; brille à côté.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
@@ -3453,7 +3456,7 @@
 narrateur|Elle s'approche de la balance.
 papa|Vous avez pris le temps.
 narrateur|La goutte jaune n'est plus qu'un trait.
-narrateur|Le citron attend, et le grain brille à côté.</t>
+narrateur|Le citron attend, et le grain de cannelle brille à côté.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -3668,17 +3671,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Le citron a failli rouler, tout à l'heure. On l'a pesé. Le stand est à nous. Vous avez offert le fruit. Le métal a deux traces de doigts. La goutte jaune a quitté le zeste. Le bois de l'étal redevient sec. Deux doigts ont coincé le grain entre le métal et le zeste.</t>
+          <t>Le citron a failli rouler, tout à l'heure. On l'a pesé. Le stand est à nous. Vous avez offert le fruit. Le métal a deux traces de doigts. La goutte jaune a quitté le zeste. Le bois de l'étal redevient sec. Deux doigts ont coincé le grain de cannelle entre métal et zeste.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le citron a failli rouler, tout à l'heure. On l'a pesé. Le stand est à nous. Vous avez offert le fruit. Le métal a deux traces de doigts. La goutte jaune a quitté le zeste. Le bois de l'étal redevient sec. Deux doigts ont coincé le grain entre le métal et le zeste.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le citron a failli rouler, tout à l'heure. On l'a pesé. Le stand est à nous. Vous avez offert le fruit. Le métal a deux traces de doigts. La goutte jaune a quitté le zeste. Le bois de l'étal redevient sec. Deux doigts ont coincé le &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; entre métal et zeste.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le citron a failli rouler, tout à l'heure. On l'a pesé. Le stand est à nous. Vous avez offert le fruit. Le métal a deux traces de doigts. La goutte jaune a quitté le zeste. Le bois de l'étal redevient sec. Deux doigts ont coincé le grain entre le métal et le zeste.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le citron a failli rouler, tout à l'heure. On l'a pesé. Le stand est à nous. Vous avez offert le fruit. Le métal a deux traces de doigts. La goutte jaune a quitté le zeste. Le bois de l'étal redevient sec. Deux doigts ont coincé le &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; entre métal et zeste.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
@@ -3823,7 +3826,7 @@
 maman|Le métal a deux traces de doigts.
 narrateur|La goutte jaune a quitté le zeste.
 narrateur|Le bois de l'étal redevient sec.
-narrateur|Deux doigts ont coincé le grain entre le métal et le zeste.</t>
+narrateur|Deux doigts ont coincé le grain de cannelle entre métal et zeste.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -4428,17 +4431,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Le sac a failli se fermer trop tôt. Mila reste au bord, le nez sur le papier. Tu as regardé le fond. Oui. Le papier est resté ouvert. Le zeste habite le brun. La goutte jaune a séché sur le pli. Le sac brun garde une ombre de citron, et le grain.</t>
+          <t>Le sac a failli se fermer trop tôt. Mila reste au bord, le nez sur le papier. Tu as regardé le fond. Oui. Le papier est resté ouvert. Le zeste habite le brun. La goutte jaune a séché sur le pli. Le sac brun garde une ombre de citron, et le grain de cannelle.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le sac a failli se fermer trop tôt. Mila reste au bord, le nez sur le papier. Tu as regardé le fond. Oui. Le papier est resté ouvert. Le zeste habite le brun. La goutte jaune a séché sur le pli. Le sac brun garde une ombre de citron, et le grain.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le sac a failli se fermer trop tôt. Mila reste au bord, le nez sur le papier. Tu as regardé le fond. Oui. Le papier est resté ouvert. Le zeste habite le brun. La goutte jaune a séché sur le pli. Le sac brun garde une ombre de citron, et le &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le sac a failli se fermer trop tôt. Mila reste au bord, le nez sur le papier. Tu as regardé le fond. Oui. Le papier est resté ouvert. Le zeste habite le brun. La goutte jaune a séché sur le pli. Le sac brun garde une ombre de citron, et le grain.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le sac a failli se fermer trop tôt. Mila reste au bord, le nez sur le papier. Tu as regardé le fond. Oui. Le papier est resté ouvert. Le zeste habite le brun. La goutte jaune a séché sur le pli. Le sac brun garde une ombre de citron, et le &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt;.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
@@ -4583,7 +4586,7 @@
 papa|Le papier est resté ouvert.
 maman|Le zeste habite le brun.
 narrateur|La goutte jaune a séché sur le pli.
-narrateur|Le sac brun garde une ombre de citron, et le grain.</t>
+narrateur|Le sac brun garde une ombre de citron, et le grain de cannelle.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -4798,17 +4801,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Mila revient, un sac d'un autre étal à la main. Maintenant ? Oui, le tien est là. Elle s'approche du papier. Vous avez pris le temps. Le sac l'attendait. La goutte jaune a quitté le col. Le papier reste ouvert, le grain au bord.</t>
+          <t>Mila revient, un sac d'un autre étal à la main. Maintenant ? Oui, le tien est là. Elle s'approche du papier. Vous avez pris le temps. Le sac l'attendait. La goutte jaune a quitté le col. Le papier reste ouvert, le grain de cannelle au bord.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Mila revient, un sac d'un autre étal à la main. Maintenant ? Oui, le tien est là. Elle s'approche du papier. Vous avez pris le temps. Le sac l'attendait. La goutte jaune a quitté le col. Le papier reste ouvert, le grain au bord.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Mila revient, un sac d'un autre étal à la main. Maintenant ? Oui, le tien est là. Elle s'approche du papier. Vous avez pris le temps. Le sac l'attendait. La goutte jaune a quitté le col. Le papier reste ouvert, le &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; au bord.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Mila revient, un sac d'un autre étal à la main. Maintenant ? Oui, le tien est là. Elle s'approche du papier. Vous avez pris le temps. Le sac l'attendait. La goutte jaune a quitté le col. Le papier reste ouvert, le grain au bord.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Mila revient, un sac d'un autre étal à la main. Maintenant ? Oui, le tien est là. Elle s'approche du papier. Vous avez pris le temps. Le sac l'attendait. La goutte jaune a quitté le col. Le papier reste ouvert, le &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; au bord.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -4953,7 +4956,7 @@
 papa|Vous avez pris le temps.
 maman|Le sac l'attendait.
 narrateur|La goutte jaune a quitté le col.
-narrateur|Le papier reste ouvert, le grain au bord.</t>
+narrateur|Le papier reste ouvert, le grain de cannelle au bord.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -5168,17 +5171,17 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Le papier a failli se fendre jusqu'au bout. On l'a porté. Le stand est à nous. Vous avez offert le fruit. Le sac penche entre deux petites mains. La goutte jaune a séché dans le fond. Le bois de l'étal redevient sec. Le sac penche entre deux petites mains, grain au fond.</t>
+          <t>Le papier a failli se fendre jusqu'au bout. On l'a porté. Le stand est à nous. Vous avez offert le fruit. Le sac penche entre deux petites mains. La goutte jaune a séché dans le fond. Le bois de l'étal redevient sec. Le sac penche entre deux petites mains, grain de cannelle au fond.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le papier a failli se fendre jusqu'au bout. On l'a porté. Le stand est à nous. Vous avez offert le fruit. Le sac penche entre deux petites mains. La goutte jaune a séché dans le fond. Le bois de l'étal redevient sec. Le sac penche entre deux petites mains, grain au fond.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le papier a failli se fendre jusqu'au bout. On l'a porté. Le stand est à nous. Vous avez offert le fruit. Le sac penche entre deux petites mains. La goutte jaune a séché dans le fond. Le bois de l'étal redevient sec. Le sac penche entre deux petites mains, &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; au fond.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le papier a failli se fendre jusqu'au bout. On l'a porté. Le stand est à nous. Vous avez offert le fruit. Le sac penche entre deux petites mains. La goutte jaune a séché dans le fond. Le bois de l'étal redevient sec. Le sac penche entre deux petites mains, grain au fond.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le papier a failli se fendre jusqu'au bout. On l'a porté. Le stand est à nous. Vous avez offert le fruit. Le sac penche entre deux petites mains. La goutte jaune a séché dans le fond. Le bois de l'étal redevient sec. Le sac penche entre deux petites mains, &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; au fond.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
@@ -5323,7 +5326,7 @@
 maman|Le sac penche entre deux petites mains.
 narrateur|La goutte jaune a séché dans le fond.
 narrateur|Le bois de l'étal redevient sec.
-narrateur|Le sac penche entre deux petites mains, grain au fond.</t>
+narrateur|Le sac penche entre deux petites mains, grain de cannelle au fond.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -5928,17 +5931,17 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>La tour a failli tout emporter. Mila reste au bord, les yeux sur le bas. Tu as regardé en bas. Oui. Les citrons du haut brillent, trop loin. Le bois d'en bas est à sa hauteur. La goutte jaune a séché sur la planche. Les citrons du haut brillent, grain sur le bord.</t>
+          <t>La tour a failli tout emporter. Mila reste au bord, les yeux sur le bas. Tu as regardé en bas. Oui. Les citrons du haut brillent, trop loin. Le bois d'en bas est à sa hauteur. La goutte jaune a séché sur la planche. Les citrons du haut brillent, grain de cannelle sur le bord.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La tour a failli tout emporter. Mila reste au bord, les yeux sur le bas. Tu as regardé en bas. Oui. Les citrons du haut brillent, trop loin. Le bois d'en bas est à sa hauteur. La goutte jaune a séché sur la planche. Les citrons du haut brillent, grain sur le bord.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La tour a failli tout emporter. Mila reste au bord, les yeux sur le bas. Tu as regardé en bas. Oui. Les citrons du haut brillent, trop loin. Le bois d'en bas est à sa hauteur. La goutte jaune a séché sur la planche. Les citrons du haut brillent, &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; sur le bord.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La tour a failli tout emporter. Mila reste au bord, les yeux sur le bas. Tu as regardé en bas. Oui. Les citrons du haut brillent, trop loin. Le bois d'en bas est à sa hauteur. La goutte jaune a séché sur la planche. Les citrons du haut brillent, grain sur le bord.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La tour a failli tout emporter. Mila reste au bord, les yeux sur le bas. Tu as regardé en bas. Oui. Les citrons du haut brillent, trop loin. Le bois d'en bas est à sa hauteur. La goutte jaune a séché sur la planche. Les citrons du haut brillent, &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; sur le bord.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
@@ -6083,7 +6086,7 @@
 papa|Les citrons du haut brillent, trop loin.
 maman|Le bois d'en bas est à sa hauteur.
 narrateur|La goutte jaune a séché sur la planche.
-narrateur|Les citrons du haut brillent, grain sur le bord.</t>
+narrateur|Les citrons du haut brillent, grain de cannelle sur le bord.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -6298,17 +6301,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Mila revient, les poches un peu moins profondes. Maintenant ? Oui, ta place est là. Elle s'approche de la caisse. Vous avez pris le temps. La place vide l'attendait. La goutte jaune a quitté le bord. Une place vide reste, le grain posé dessus.</t>
+          <t>Mila revient, les poches un peu moins profondes. Maintenant ? Oui, ta place est là. Elle s'approche de la caisse. Vous avez pris le temps. La place vide l'attendait. La goutte jaune a quitté le bord. Une place vide reste, le grain de cannelle posé dessus.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Mila revient, les poches un peu moins profondes. Maintenant ? Oui, ta place est là. Elle s'approche de la caisse. Vous avez pris le temps. La place vide l'attendait. La goutte jaune a quitté le bord. Une place vide reste, le grain posé dessus.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Mila revient, les poches un peu moins profondes. Maintenant ? Oui, ta place est là. Elle s'approche de la caisse. Vous avez pris le temps. La place vide l'attendait. La goutte jaune a quitté le bord. Une place vide reste, le &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; posé dessus.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Mila revient, les poches un peu moins profondes. Maintenant ? Oui, ta place est là. Elle s'approche de la caisse. Vous avez pris le temps. La place vide l'attendait. La goutte jaune a quitté le bord. Une place vide reste, le grain posé dessus.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Mila revient, les poches un peu moins profondes. Maintenant ? Oui, ta place est là. Elle s'approche de la caisse. Vous avez pris le temps. La place vide l'attendait. La goutte jaune a quitté le bord. Une place vide reste, le &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; posé dessus.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -6453,7 +6456,7 @@
 papa|Vous avez pris le temps.
 maman|La place vide l'attendait.
 narrateur|La goutte jaune a quitté le bord.
-narrateur|Une place vide reste, le grain posé dessus.</t>
+narrateur|Une place vide reste, le grain de cannelle posé dessus.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -6668,17 +6671,17 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Le citron a failli tomber de la tour. On l'a rangé. Le stand est à nous. Vous avez offert le fruit. La tour tient, plus basse. La goutte jaune a séché sur le zeste. Le bois de l'étal redevient sec. Le citron mouillé a rejoint la tour, grain collé.</t>
+          <t>Le citron a failli tomber de la tour. On l'a rangé. Le stand est à nous. Vous avez offert le fruit. La tour tient, plus basse. La goutte jaune a séché sur le zeste. Le bois de l'étal redevient sec. Le citron mouillé a rejoint la tour, grain de cannelle collé.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le citron a failli tomber de la tour. On l'a rangé. Le stand est à nous. Vous avez offert le fruit. La tour tient, plus basse. La goutte jaune a séché sur le zeste. Le bois de l'étal redevient sec. Le citron mouillé a rejoint la tour, grain collé.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le citron a failli tomber de la tour. On l'a rangé. Le stand est à nous. Vous avez offert le fruit. La tour tient, plus basse. La goutte jaune a séché sur le zeste. Le bois de l'étal redevient sec. Le citron mouillé a rejoint la tour, &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; collé.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le citron a failli tomber de la tour. On l'a rangé. Le stand est à nous. Vous avez offert le fruit. La tour tient, plus basse. La goutte jaune a séché sur le zeste. Le bois de l'étal redevient sec. Le citron mouillé a rejoint la tour, grain collé.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le citron a failli tomber de la tour. On l'a rangé. Le stand est à nous. Vous avez offert le fruit. La tour tient, plus basse. La goutte jaune a séché sur le zeste. Le bois de l'étal redevient sec. Le citron mouillé a rejoint la tour, &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; collé.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -6823,7 +6826,7 @@
 maman|La tour tient, plus basse.
 narrateur|La goutte jaune a séché sur le zeste.
 narrateur|Le bois de l'étal redevient sec.
-narrateur|Le citron mouillé a rejoint la tour, grain collé.</t>
+narrateur|Le citron mouillé a rejoint la tour, grain de cannelle collé.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
@@ -6855,17 +6858,17 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Raphaël passe sous le store rouge. La toile chauffe les joues, d'une lumière rose. Les fraises sentent le sucre. La balance, le sac et la caisse restent là. Il saisit une fraise, trop vite. Pour toi, Mila ! Mila serre les poches. La fraise brille, seule, entre ses doigts. L'élan de Raphaël se casse. Elle n'a pas ouvert la main. Papa s'accroupit, au ras de la barquette. Une goutte rose glisse le long de la toile. Elle mouille le grain de cannelle, au bord. Il pique un peu, le grain. Tu le sens, sur le bois ?</t>
+          <t>Raphaël passe sous le store rouge. La toile chauffe les joues, d'une lumière rose. Les fraises sentent le sucre. La balance, le sac et la caisse restent là. Il saisit une fraise, trop vite. Pour toi, Mila ! Mila serre les poches. La fraise brille, seule, entre ses doigts. L'élan de Raphaël se casse. Elle n'a pas ouvert la main. Papa s'accroupit, au ras de la barquette. Une goutte rose glisse le long de la toile. Elle mouille le grain de cannelle, au bord. Il pique un peu, le grain. Tu le sens, sur le bois ? Une femme passe, le nez ailleurs.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Raphaël passe sous le &lt;emphasis level="moderate"&gt;store rouge&lt;/emphasis&gt;. La toile chauffe les joues, d'une lumière rose. Les fraises sentent le sucre. La balance, le sac et la caisse restent là. Il saisit une fraise, trop vite. Pour toi, Mila ! Mila serre les poches. La fraise brille, seule, entre ses doigts. L'élan de Raphaël se casse. Elle n'a pas ouvert la main. Papa s'accroupit, au ras de la barquette. Une goutte rose glisse le long de la toile. Elle mouille le grain de cannelle, au bord. Il pique un peu, le grain. Tu le sens, sur le bois ?&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Raphaël passe sous le &lt;emphasis level="moderate"&gt;store rouge&lt;/emphasis&gt;. La toile chauffe les joues, d'une lumière rose. Les fraises sentent le sucre. La balance, le sac et la caisse restent là. Il saisit une fraise, trop vite. Pour toi, Mila ! Mila serre les poches. La fraise brille, seule, entre ses doigts. L'élan de Raphaël se casse. Elle n'a pas ouvert la main. Papa s'accroupit, au ras de la barquette. Une goutte rose glisse le long de la toile. Elle mouille le grain de cannelle, au bord. Il pique un peu, le grain. Tu le sens, sur le bois ? Une femme passe, le nez ailleurs.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Raphaël passe sous le &lt;emphasis&gt;store rouge&lt;/emphasis&gt;. La toile chauffe les joues, d'une lumière rose. Les fraises sentent le sucre. La balance, le sac et la caisse restent là. Il saisit une fraise, trop vite. Pour toi, Mila ! Mila serre les poches. La fraise brille, seule, entre ses doigts. L'élan de Raphaël se casse. Elle n'a pas ouvert la main. Papa s'accroupit, au ras de la barquette. Une goutte rose glisse le long de la toile. Elle mouille le grain de cannelle, au bord. Il pique un peu, le grain. Tu le sens, sur le bois ? [pause]</t>
+          <t>Raphaël passe sous le &lt;emphasis&gt;store rouge&lt;/emphasis&gt;. La toile chauffe les joues, d'une lumière rose. Les fraises sentent le sucre. La balance, le sac et la caisse restent là. Il saisit une fraise, trop vite. Pour toi, Mila ! Mila serre les poches. La fraise brille, seule, entre ses doigts. L'élan de Raphaël se casse. Elle n'a pas ouvert la main. Papa s'accroupit, au ras de la barquette. Une goutte rose glisse le long de la toile. Elle mouille le grain de cannelle, au bord. Il pique un peu, le grain. Tu le sens, sur le bois ? Une femme passe, le nez ailleurs. [pause]</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
@@ -7013,7 +7016,8 @@
 narrateur|Une goutte rose glisse le long de la toile.
 narrateur|Elle mouille le grain de cannelle, au bord.
 enfant-m|Il pique un peu, le grain.
-maman|Tu le sens, sur le bois ?</t>
+maman|Tu le sens, sur le bois ?
+narrateur|Une femme passe, le nez ailleurs.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -8185,17 +8189,17 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Le jus a failli emporter le grain. Mila reste au bord, les yeux sur le rond. Tu as regardé le tic. Oui. L'aiguille s'est tue. La fraise a gardé sa place. La goutte rose a séché en rond mince. Un rond rose sèche, le grain au centre.</t>
+          <t>Le jus a failli emporter le grain. Mila reste au bord, les yeux sur le rond. Tu as regardé le tic. Oui. L'aiguille s'est tue. La fraise a gardé sa place. La goutte rose a séché en rond mince. Un rond rose sèche, le grain de cannelle au centre.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le jus a failli emporter le grain. Mila reste au bord, les yeux sur le rond. Tu as regardé le tic. Oui. L'aiguille s'est tue. La fraise a gardé sa place. La goutte rose a séché en rond mince. Un rond rose sèche, le grain au centre.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le jus a failli emporter le grain. Mila reste au bord, les yeux sur le rond. Tu as regardé le tic. Oui. L'aiguille s'est tue. La fraise a gardé sa place. La goutte rose a séché en rond mince. Un rond rose sèche, le &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; au centre.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le jus a failli emporter le grain. Mila reste au bord, les yeux sur le rond. Tu as regardé le tic. Oui. L'aiguille s'est tue. La fraise a gardé sa place. La goutte rose a séché en rond mince. Un rond rose sèche, le grain au centre.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le jus a failli emporter le grain. Mila reste au bord, les yeux sur le rond. Tu as regardé le tic. Oui. L'aiguille s'est tue. La fraise a gardé sa place. La goutte rose a séché en rond mince. Un rond rose sèche, le &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; au centre.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
@@ -8340,7 +8344,7 @@
 papa|L'aiguille s'est tue.
 maman|La fraise a gardé sa place.
 narrateur|La goutte rose a séché en rond mince.
-narrateur|Un rond rose sèche, le grain au centre.</t>
+narrateur|Un rond rose sèche, le grain de cannelle au centre.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -8372,17 +8376,17 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Plus tard. D'accord. Je te la garde. Raphaël garde la fraise sur le métal. Mila recule vers une odeur de pain, plus loin. La fraise garde sa place. Le grain de cannelle attend, à côté du fruit. Le plateau reste froid, pour elle.</t>
+          <t>Plus tard. D'accord. Je te la garde. Raphaël garde la fraise sur le métal. Mila recule vers une autre odeur, plus loin. La fraise garde sa place. Le grain de cannelle attend, à côté du fruit. Le plateau reste froid, pour elle.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Plus tard. D'accord. Je te la garde. Raphaël garde la fraise sur le métal. Mila recule vers une odeur de pain, plus loin. La fraise garde sa place. Le grain de cannelle attend, à côté du fruit. Le plateau reste froid, pour elle.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Plus tard. D'accord. Je te la garde. Raphaël garde la fraise sur le métal. Mila recule vers une autre odeur, plus loin. La fraise garde sa place. Le grain de cannelle attend, à côté du fruit. Le plateau reste froid, pour elle.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Plus tard. D'accord. Je te la garde. Raphaël garde la fraise sur le métal. Mila recule vers une odeur de pain, plus loin. La fraise garde sa place. Le grain de cannelle attend, à côté du fruit. Le plateau reste froid, pour elle. [pause]</t>
+          <t>Plus tard. D'accord. Je te la garde. Raphaël garde la fraise sur le métal. Mila recule vers une autre odeur, plus loin. La fraise garde sa place. Le grain de cannelle attend, à côté du fruit. Le plateau reste froid, pour elle. [pause]</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -8520,7 +8524,7 @@
 enfant-m|D'accord.
 enfant-m|Je te la garde.
 narrateur|Raphaël garde la fraise sur le métal.
-narrateur|Mila recule vers une odeur de pain, plus loin.
+narrateur|Mila recule vers une autre odeur, plus loin.
 maman|La fraise garde sa place.
 narrateur|Le grain de cannelle attend, à côté du fruit.
 papa|Le plateau reste froid, pour elle.</t>
@@ -8555,17 +8559,17 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Mila revient, une miette de pain au coin des lèvres. Maintenant ? Oui. Elle s'approche de la balance. Vous avez pris le temps. La fraise l'attendait. La goutte rose n'est plus qu'un halo. La fraise garde sa place, grain à côté.</t>
+          <t>Mila revient, une miette sucrée au coin des lèvres. Maintenant ? Oui. Elle s'approche de la balance. Vous avez pris le temps. La fraise l'attendait. La goutte rose n'est plus qu'un halo. La fraise garde sa place, grain de cannelle à côté.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Mila revient, une miette de pain au coin des lèvres. Maintenant ? Oui. Elle s'approche de la balance. Vous avez pris le temps. La fraise l'attendait. La goutte rose n'est plus qu'un halo. La fraise garde sa place, grain à côté.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Mila revient, une miette sucrée au coin des lèvres. Maintenant ? Oui. Elle s'approche de la balance. Vous avez pris le temps. La fraise l'attendait. La goutte rose n'est plus qu'un halo. La fraise garde sa place, &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; à côté.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Mila revient, une miette de pain au coin des lèvres. Maintenant ? Oui. Elle s'approche de la balance. Vous avez pris le temps. La fraise l'attendait. La goutte rose n'est plus qu'un halo. La fraise garde sa place, grain à côté.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Mila revient, une miette sucrée au coin des lèvres. Maintenant ? Oui. Elle s'approche de la balance. Vous avez pris le temps. La fraise l'attendait. La goutte rose n'est plus qu'un halo. La fraise garde sa place, &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; à côté.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -8703,14 +8707,14 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|Mila revient, une miette de pain au coin des lèvres.
+          <t>narrateur|Mila revient, une miette sucrée au coin des lèvres.
 enfant-f|Maintenant ?
 enfant-m|Oui.
 narrateur|Elle s'approche de la balance.
 papa|Vous avez pris le temps.
 maman|La fraise l'attendait.
 narrateur|La goutte rose n'est plus qu'un halo.
-narrateur|La fraise garde sa place, grain à côté.</t>
+narrateur|La fraise garde sa place, grain de cannelle à côté.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -8925,17 +8929,17 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>La fraise a failli glisser dans le jus. On l'a pesée. Le stand est à nous. Vous avez offert le fruit. Deux doigts ont gardé le grain. La goutte rose a quitté le métal. Le bois de l'étal redevient sec. L'aiguille s'est tue, grain sous deux doigts.</t>
+          <t>La fraise a failli glisser dans le jus. On l'a pesée. Le stand est à nous. Vous avez offert le fruit. Deux doigts ont gardé le grain. La goutte rose a quitté le métal. Le bois de l'étal redevient sec. L'aiguille s'est tue, grain de cannelle sous deux doigts.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La fraise a failli glisser dans le jus. On l'a pesée. Le stand est à nous. Vous avez offert le fruit. Deux doigts ont gardé le grain. La goutte rose a quitté le métal. Le bois de l'étal redevient sec. L'aiguille s'est tue, grain sous deux doigts.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La fraise a failli glisser dans le jus. On l'a pesée. Le stand est à nous. Vous avez offert le fruit. Deux doigts ont gardé le grain. La goutte rose a quitté le métal. Le bois de l'étal redevient sec. L'aiguille s'est tue, &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; sous deux doigts.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La fraise a failli glisser dans le jus. On l'a pesée. Le stand est à nous. Vous avez offert le fruit. Deux doigts ont gardé le grain. La goutte rose a quitté le métal. Le bois de l'étal redevient sec. L'aiguille s'est tue, grain sous deux doigts.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La fraise a failli glisser dans le jus. On l'a pesée. Le stand est à nous. Vous avez offert le fruit. Deux doigts ont gardé le grain. La goutte rose a quitté le métal. Le bois de l'étal redevient sec. L'aiguille s'est tue, &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; sous deux doigts.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -9080,7 +9084,7 @@
 maman|Deux doigts ont gardé le grain.
 narrateur|La goutte rose a quitté le métal.
 narrateur|Le bois de l'étal redevient sec.
-narrateur|L'aiguille s'est tue, grain sous deux doigts.</t>
+narrateur|L'aiguille s'est tue, grain de cannelle sous deux doigts.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -9685,17 +9689,17 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Le sac a failli avaler le grain. Mila reste au bord, le nez dans le pli. Tu as regardé le pli. Oui. Le papier est resté ouvert. Le sucre habite le brun. La goutte rose a séché dans le pli. Le sac sent le sucre, grain coincé dans le pli.</t>
+          <t>Le sac a failli avaler le grain. Mila reste au bord, le nez dans le pli. Tu as regardé le pli. Oui. Le papier est resté ouvert. Le sucre habite le brun. La goutte rose a séché dans le pli. Le sac sent le sucre, grain de cannelle coincé dans le pli.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le sac a failli avaler le grain. Mila reste au bord, le nez dans le pli. Tu as regardé le pli. Oui. Le papier est resté ouvert. Le sucre habite le brun. La goutte rose a séché dans le pli. Le sac sent le sucre, grain coincé dans le pli.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le sac a failli avaler le grain. Mila reste au bord, le nez dans le pli. Tu as regardé le pli. Oui. Le papier est resté ouvert. Le sucre habite le brun. La goutte rose a séché dans le pli. Le sac sent le sucre, &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; coincé dans le pli.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le sac a failli avaler le grain. Mila reste au bord, le nez dans le pli. Tu as regardé le pli. Oui. Le papier est resté ouvert. Le sucre habite le brun. La goutte rose a séché dans le pli. Le sac sent le sucre, grain coincé dans le pli.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le sac a failli avaler le grain. Mila reste au bord, le nez dans le pli. Tu as regardé le pli. Oui. Le papier est resté ouvert. Le sucre habite le brun. La goutte rose a séché dans le pli. Le sac sent le sucre, &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; coincé dans le pli.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -9840,7 +9844,7 @@
 papa|Le papier est resté ouvert.
 maman|Le sucre habite le brun.
 narrateur|La goutte rose a séché dans le pli.
-narrateur|Le sac sent le sucre, grain coincé dans le pli.</t>
+narrateur|Le sac sent le sucre, grain de cannelle coincé dans le pli.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
@@ -10055,17 +10059,17 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Mila revient, les doigts un peu collants. Maintenant ? Oui, le sac est là. Elle s'approche du papier. Vous avez pris le temps. La barquette l'attendait. La goutte rose a quitté le col. La barquette attend, grain sur le papier.</t>
+          <t>Mila revient, les doigts un peu collants. Maintenant ? Oui, le sac est là. Elle s'approche du papier. Vous avez pris le temps. La barquette l'attendait. La goutte rose a quitté le col. La barquette attend, grain de cannelle sur le papier.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Mila revient, les doigts un peu collants. Maintenant ? Oui, le sac est là. Elle s'approche du papier. Vous avez pris le temps. La barquette l'attendait. La goutte rose a quitté le col. La barquette attend, grain sur le papier.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Mila revient, les doigts un peu collants. Maintenant ? Oui, le sac est là. Elle s'approche du papier. Vous avez pris le temps. La barquette l'attendait. La goutte rose a quitté le col. La barquette attend, &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; sur le papier.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Mila revient, les doigts un peu collants. Maintenant ? Oui, le sac est là. Elle s'approche du papier. Vous avez pris le temps. La barquette l'attendait. La goutte rose a quitté le col. La barquette attend, grain sur le papier.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Mila revient, les doigts un peu collants. Maintenant ? Oui, le sac est là. Elle s'approche du papier. Vous avez pris le temps. La barquette l'attendait. La goutte rose a quitté le col. La barquette attend, &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; sur le papier.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -10210,7 +10214,7 @@
 papa|Vous avez pris le temps.
 maman|La barquette l'attendait.
 narrateur|La goutte rose a quitté le col.
-narrateur|La barquette attend, grain sur le papier.</t>
+narrateur|La barquette attend, grain de cannelle sur le papier.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
@@ -10425,17 +10429,17 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Les fraises ont failli s'écraser au fond. On l'a porté. Le stand est à nous. Vous avez offert le fruit. Le sac froisse, porté à deux. La goutte rose a séché au fond. Le bois de l'étal redevient sec. Le sac froisse, porté à deux, grain dedans.</t>
+          <t>Les fraises ont failli s'écraser au fond. On l'a porté. Le stand est à nous. Vous avez offert le fruit. Le sac froisse, porté à deux. La goutte rose a séché au fond. Le bois de l'étal redevient sec. Le sac froisse, porté à deux, grain de cannelle dedans.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Les fraises ont failli s'écraser au fond. On l'a porté. Le stand est à nous. Vous avez offert le fruit. Le sac froisse, porté à deux. La goutte rose a séché au fond. Le bois de l'étal redevient sec. Le sac froisse, porté à deux, grain dedans.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Les fraises ont failli s'écraser au fond. On l'a porté. Le stand est à nous. Vous avez offert le fruit. Le sac froisse, porté à deux. La goutte rose a séché au fond. Le bois de l'étal redevient sec. Le sac froisse, porté à deux, &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; dedans.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Les fraises ont failli s'écraser au fond. On l'a porté. Le stand est à nous. Vous avez offert le fruit. Le sac froisse, porté à deux. La goutte rose a séché au fond. Le bois de l'étal redevient sec. Le sac froisse, porté à deux, grain dedans.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Les fraises ont failli s'écraser au fond. On l'a porté. Le stand est à nous. Vous avez offert le fruit. Le sac froisse, porté à deux. La goutte rose a séché au fond. Le bois de l'étal redevient sec. Le sac froisse, porté à deux, &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; dedans.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
@@ -10580,7 +10584,7 @@
 maman|Le sac froisse, porté à deux.
 narrateur|La goutte rose a séché au fond.
 narrateur|Le bois de l'étal redevient sec.
-narrateur|Le sac froisse, porté à deux, grain dedans.</t>
+narrateur|Le sac froisse, porté à deux, grain de cannelle dedans.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
@@ -11185,17 +11189,17 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>La rangée a failli tout emporter. Mila reste au bord, les yeux sur le bois. Tu as regardé la place. Oui. Les fraises sont alignées, sous le rouge. Le bois a gardé un creux. La goutte rose a séché sur la planche. Les fraises sont alignées, grain sur le bois rouge.</t>
+          <t>La rangée a failli tout emporter. Mila reste au bord, les yeux sur le bois. Tu as regardé la place. Oui. Les fraises sont alignées, sous le rouge. Le bois a gardé un creux. La goutte rose a séché sur la planche. Les fraises sont alignées, grain de cannelle sur le bois rouge.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La rangée a failli tout emporter. Mila reste au bord, les yeux sur le bois. Tu as regardé la place. Oui. Les fraises sont alignées, sous le rouge. Le bois a gardé un creux. La goutte rose a séché sur la planche. Les fraises sont alignées, grain sur le bois rouge.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La rangée a failli tout emporter. Mila reste au bord, les yeux sur le bois. Tu as regardé la place. Oui. Les fraises sont alignées, sous le rouge. Le bois a gardé un creux. La goutte rose a séché sur la planche. Les fraises sont alignées, &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; sur le bois rouge.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La rangée a failli tout emporter. Mila reste au bord, les yeux sur le bois. Tu as regardé la place. Oui. Les fraises sont alignées, sous le rouge. Le bois a gardé un creux. La goutte rose a séché sur la planche. Les fraises sont alignées, grain sur le bois rouge.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La rangée a failli tout emporter. Mila reste au bord, les yeux sur le bois. Tu as regardé la place. Oui. Les fraises sont alignées, sous le rouge. Le bois a gardé un creux. La goutte rose a séché sur la planche. Les fraises sont alignées, &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; sur le bois rouge.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -11340,7 +11344,7 @@
 papa|Les fraises sont alignées, sous le rouge.
 maman|Le bois a gardé un creux.
 narrateur|La goutte rose a séché sur la planche.
-narrateur|Les fraises sont alignées, grain sur le bois rouge.</t>
+narrateur|Les fraises sont alignées, grain de cannelle sur le bois rouge.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
@@ -11555,17 +11559,17 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Mila revient, une main hors de la poche. Maintenant ? Oui, ta place est là. Elle s'approche de la caisse. Vous avez pris le temps. La place rose l'attendait. La goutte rose a quitté le bord. Une place rose reste, grain au creux.</t>
+          <t>Mila revient, une main hors de la poche. Maintenant ? Oui, ta place est là. Elle s'approche de la caisse. Vous avez pris le temps. La place rose l'attendait. La goutte rose a quitté le bord. Une place rose reste, grain de cannelle au creux.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Mila revient, une main hors de la poche. Maintenant ? Oui, ta place est là. Elle s'approche de la caisse. Vous avez pris le temps. La place rose l'attendait. La goutte rose a quitté le bord. Une place rose reste, grain au creux.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Mila revient, une main hors de la poche. Maintenant ? Oui, ta place est là. Elle s'approche de la caisse. Vous avez pris le temps. La place rose l'attendait. La goutte rose a quitté le bord. Une place rose reste, &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; au creux.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Mila revient, une main hors de la poche. Maintenant ? Oui, ta place est là. Elle s'approche de la caisse. Vous avez pris le temps. La place rose l'attendait. La goutte rose a quitté le bord. Une place rose reste, grain au creux.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Mila revient, une main hors de la poche. Maintenant ? Oui, ta place est là. Elle s'approche de la caisse. Vous avez pris le temps. La place rose l'attendait. La goutte rose a quitté le bord. Une place rose reste, &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; au creux.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -11710,7 +11714,7 @@
 papa|Vous avez pris le temps.
 maman|La place rose l'attendait.
 narrateur|La goutte rose a quitté le bord.
-narrateur|Une place rose reste, grain au creux.</t>
+narrateur|Une place rose reste, grain de cannelle au creux.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
@@ -11925,17 +11929,17 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>La fraise a failli rouler hors de la caisse. On l'a rangée. Le stand est à nous. Vous avez offert le fruit. La rangée tient, fermée. La goutte rose a séché sur le fruit. Le bois de l'étal redevient sec. La fraise rattrapée ne roule plus, grain dessus.</t>
+          <t>La fraise a failli rouler hors de la caisse. On l'a rangée. Le stand est à nous. Vous avez offert le fruit. La rangée tient, fermée. La goutte rose a séché sur le fruit. Le bois de l'étal redevient sec. La fraise rattrapée ne roule plus, grain de cannelle dessus.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La fraise a failli rouler hors de la caisse. On l'a rangée. Le stand est à nous. Vous avez offert le fruit. La rangée tient, fermée. La goutte rose a séché sur le fruit. Le bois de l'étal redevient sec. La fraise rattrapée ne roule plus, grain dessus.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La fraise a failli rouler hors de la caisse. On l'a rangée. Le stand est à nous. Vous avez offert le fruit. La rangée tient, fermée. La goutte rose a séché sur le fruit. Le bois de l'étal redevient sec. La fraise rattrapée ne roule plus, &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; dessus.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La fraise a failli rouler hors de la caisse. On l'a rangée. Le stand est à nous. Vous avez offert le fruit. La rangée tient, fermée. La goutte rose a séché sur le fruit. Le bois de l'étal redevient sec. La fraise rattrapée ne roule plus, grain dessus.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La fraise a failli rouler hors de la caisse. On l'a rangée. Le stand est à nous. Vous avez offert le fruit. La rangée tient, fermée. La goutte rose a séché sur le fruit. Le bois de l'étal redevient sec. La fraise rattrapée ne roule plus, &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; dessus.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -12080,7 +12084,7 @@
 maman|La rangée tient, fermée.
 narrateur|La goutte rose a séché sur le fruit.
 narrateur|Le bois de l'étal redevient sec.
-narrateur|La fraise rattrapée ne roule plus, grain dessus.</t>
+narrateur|La fraise rattrapée ne roule plus, grain de cannelle dessus.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
@@ -12112,17 +12116,17 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Raphaël s'abrite sous le store vert. La toile pose des taches vertes sur les poires. Elles sont lourdes. La balance, le sac et la caisse restent là. Il soulève une poire, trop vite. Tiens, Mila ! Mila baisse les yeux. La poire pèse, seule, contre son ventre. Dans sa poitrine, ça serre, fort. Elle n'a pas levé les mains. Maman s'accroupit, à hauteur de l'étal. Une goutte verte pend, trop ronde. Elle tombe près du grain de cannelle. Le grain a un point d'eau. Tu le vois, collé au bois ?</t>
+          <t>Raphaël s'abrite sous le store vert. La toile pose des taches vertes sur les poires. Elles sont lourdes. La balance, le sac et la caisse restent là. Il soulève une poire, trop vite. Tiens, Mila ! Mila baisse les yeux. La poire pèse, seule, contre son ventre. Dans sa poitrine, ça serre, fort. Elle n'a pas levé les mains. Maman s'accroupit, à hauteur de l'étal. Une goutte verte pend, trop ronde. Elle tombe près du grain de cannelle. Le grain a un point d'eau. Tu le vois, collé au bois ? Un homme passe, sans regarder l'étal.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Raphaël s'abrite sous le &lt;emphasis level="moderate"&gt;store vert&lt;/emphasis&gt;. La toile pose des taches vertes sur les poires. Elles sont lourdes. La balance, le sac et la caisse restent là. Il soulève une poire, trop vite. Tiens, Mila ! Mila baisse les yeux. La poire pèse, seule, contre son ventre. Dans sa poitrine, ça serre, fort. Elle n'a pas levé les mains. Maman s'accroupit, à hauteur de l'étal. Une goutte verte pend, trop ronde. Elle tombe près du grain de cannelle. Le grain a un point d'eau. Tu le vois, collé au bois ?&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Raphaël s'abrite sous le &lt;emphasis level="moderate"&gt;store vert&lt;/emphasis&gt;. La toile pose des taches vertes sur les poires. Elles sont lourdes. La balance, le sac et la caisse restent là. Il soulève une poire, trop vite. Tiens, Mila ! Mila baisse les yeux. La poire pèse, seule, contre son ventre. Dans sa poitrine, ça serre, fort. Elle n'a pas levé les mains. Maman s'accroupit, à hauteur de l'étal. Une goutte verte pend, trop ronde. Elle tombe près du grain de cannelle. Le grain a un point d'eau. Tu le vois, collé au bois ? Un homme passe, sans regarder l'étal.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Raphaël s'abrite sous le &lt;emphasis&gt;store vert&lt;/emphasis&gt;. La toile pose des taches vertes sur les poires. Elles sont lourdes. La balance, le sac et la caisse restent là. Il soulève une poire, trop vite. Tiens, Mila ! Mila baisse les yeux. La poire pèse, seule, contre son ventre. Dans sa poitrine, ça serre, fort. Elle n'a pas levé les mains. Maman s'accroupit, à hauteur de l'étal. Une goutte verte pend, trop ronde. Elle tombe près du grain de cannelle. Le grain a un point d'eau. Tu le vois, collé au bois ? [pause]</t>
+          <t>Raphaël s'abrite sous le &lt;emphasis&gt;store vert&lt;/emphasis&gt;. La toile pose des taches vertes sur les poires. Elles sont lourdes. La balance, le sac et la caisse restent là. Il soulève une poire, trop vite. Tiens, Mila ! Mila baisse les yeux. La poire pèse, seule, contre son ventre. Dans sa poitrine, ça serre, fort. Elle n'a pas levé les mains. Maman s'accroupit, à hauteur de l'étal. Une goutte verte pend, trop ronde. Elle tombe près du grain de cannelle. Le grain a un point d'eau. Tu le vois, collé au bois ? Un homme passe, sans regarder l'étal. [pause]</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
@@ -12270,7 +12274,8 @@
 narrateur|Une goutte verte pend, trop ronde.
 narrateur|Elle tombe près du grain de cannelle.
 enfant-m|Le grain a un point d'eau.
-papa|Tu le vois, collé au bois ?</t>
+papa|Tu le vois, collé au bois ?
+narrateur|Un homme passe, sans regarder l'étal.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
@@ -13442,17 +13447,17 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Le plateau a failli tout verser. Mila reste au bord, les yeux sur le chiffre. Tu as regardé le chiffre. Oui. Le chiffre noir reste grand. La poire a gardé sa place. La goutte verte a séché en virgule mince. Le chiffre noir reste grand, grain contre le plateau.</t>
+          <t>Le plateau a failli tout verser. Mila reste au bord, les yeux sur le chiffre. Tu as regardé le chiffre. Oui. Le chiffre noir reste grand. La poire a gardé sa place. La goutte verte a séché en trait d'eau. Le chiffre noir reste grand, grain de cannelle contre le plateau.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le plateau a failli tout verser. Mila reste au bord, les yeux sur le chiffre. Tu as regardé le chiffre. Oui. Le chiffre noir reste grand. La poire a gardé sa place. La goutte verte a séché en virgule mince. Le chiffre noir reste grand, grain contre le plateau.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le plateau a failli tout verser. Mila reste au bord, les yeux sur le chiffre. Tu as regardé le chiffre. Oui. Le chiffre noir reste grand. La poire a gardé sa place. La goutte verte a séché en trait d'eau. Le chiffre noir reste grand, &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; contre le plateau.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le plateau a failli tout verser. Mila reste au bord, les yeux sur le chiffre. Tu as regardé le chiffre. Oui. Le chiffre noir reste grand. La poire a gardé sa place. La goutte verte a séché en virgule mince. Le chiffre noir reste grand, grain contre le plateau.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le plateau a failli tout verser. Mila reste au bord, les yeux sur le chiffre. Tu as regardé le chiffre. Oui. Le chiffre noir reste grand. La poire a gardé sa place. La goutte verte a séché en trait d'eau. Le chiffre noir reste grand, &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; contre le plateau.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -13596,8 +13601,8 @@
 enfant-f|Oui.
 papa|Le chiffre noir reste grand.
 maman|La poire a gardé sa place.
-narrateur|La goutte verte a séché en virgule mince.
-narrateur|Le chiffre noir reste grand, grain contre le plateau.</t>
+narrateur|La goutte verte a séché en trait d'eau.
+narrateur|Le chiffre noir reste grand, grain de cannelle contre le plateau.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
@@ -13812,17 +13817,17 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Mila revient, une feuille collée à la chaussure. Maintenant ? Oui. Elle s'approche de la balance. Vous avez pris le temps. La poire l'attendait. La goutte verte n'est plus qu'un point. La poire pèse, grain à l'abri sous le fruit.</t>
+          <t>Mila revient, une feuille collée à la chaussure. Maintenant ? Oui. Elle s'approche de la balance. Vous avez pris le temps. La poire l'attendait. La goutte verte n'est plus qu'un point. La poire pèse, grain de cannelle à l'abri sous le fruit.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Mila revient, une feuille collée à la chaussure. Maintenant ? Oui. Elle s'approche de la balance. Vous avez pris le temps. La poire l'attendait. La goutte verte n'est plus qu'un point. La poire pèse, grain à l'abri sous le fruit.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Mila revient, une feuille collée à la chaussure. Maintenant ? Oui. Elle s'approche de la balance. Vous avez pris le temps. La poire l'attendait. La goutte verte n'est plus qu'un point. La poire pèse, &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; à l'abri sous le fruit.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Mila revient, une feuille collée à la chaussure. Maintenant ? Oui. Elle s'approche de la balance. Vous avez pris le temps. La poire l'attendait. La goutte verte n'est plus qu'un point. La poire pèse, grain à l'abri sous le fruit.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Mila revient, une feuille collée à la chaussure. Maintenant ? Oui. Elle s'approche de la balance. Vous avez pris le temps. La poire l'attendait. La goutte verte n'est plus qu'un point. La poire pèse, &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; à l'abri sous le fruit.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -13967,7 +13972,7 @@
 papa|Vous avez pris le temps.
 maman|La poire l'attendait.
 narrateur|La goutte verte n'est plus qu'un point.
-narrateur|La poire pèse, grain à l'abri sous le fruit.</t>
+narrateur|La poire pèse, grain de cannelle à l'abri sous le fruit.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
@@ -14182,17 +14187,17 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>La poire a failli faire pencher tout le plateau. On l'a pesée. Le stand est à nous. Vous avez offert le fruit. Le plateau s'est calmé, entre eux. La goutte verte a quitté la peau. Le bois de l'étal redevient sec. Le plateau s'est calmé, grain entre eux.</t>
+          <t>La poire a failli faire pencher tout le plateau. On l'a pesée. Le stand est à nous. Vous avez offert le fruit. Le plateau s'est calmé, entre eux. La goutte verte a quitté la peau. Le bois de l'étal redevient sec. Le plateau s'est calmé, grain de cannelle entre eux.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La poire a failli faire pencher tout le plateau. On l'a pesée. Le stand est à nous. Vous avez offert le fruit. Le plateau s'est calmé, entre eux. La goutte verte a quitté la peau. Le bois de l'étal redevient sec. Le plateau s'est calmé, grain entre eux.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La poire a failli faire pencher tout le plateau. On l'a pesée. Le stand est à nous. Vous avez offert le fruit. Le plateau s'est calmé, entre eux. La goutte verte a quitté la peau. Le bois de l'étal redevient sec. Le plateau s'est calmé, &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; entre eux.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La poire a failli faire pencher tout le plateau. On l'a pesée. Le stand est à nous. Vous avez offert le fruit. Le plateau s'est calmé, entre eux. La goutte verte a quitté la peau. Le bois de l'étal redevient sec. Le plateau s'est calmé, grain entre eux.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La poire a failli faire pencher tout le plateau. On l'a pesée. Le stand est à nous. Vous avez offert le fruit. Le plateau s'est calmé, entre eux. La goutte verte a quitté la peau. Le bois de l'étal redevient sec. Le plateau s'est calmé, &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; entre eux.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -14337,7 +14342,7 @@
 maman|Le plateau s'est calmé, entre eux.
 narrateur|La goutte verte a quitté la peau.
 narrateur|Le bois de l'étal redevient sec.
-narrateur|Le plateau s'est calmé, grain entre eux.</t>
+narrateur|Le plateau s'est calmé, grain de cannelle entre eux.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
@@ -14942,17 +14947,17 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Le sac a failli se déchirer jusqu'au fond. Mila reste au bord, les yeux sur la tache. Tu as regardé le col. Oui. Le sac a pris la forme de la poire. Le sucré habite le brun. La goutte verte a séché au col. Le sac a pris la forme de la poire, grain au col.</t>
+          <t>Le sac a failli se déchirer jusqu'au fond. Mila reste au bord, les yeux sur la tache. Tu as regardé le col. Oui. Le sac a pris la forme de la poire. Le sucré habite le brun. La goutte verte a séché au col. Le sac a pris la forme de la poire, grain de cannelle au col.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le sac a failli se déchirer jusqu'au fond. Mila reste au bord, les yeux sur la tache. Tu as regardé le col. Oui. Le sac a pris la forme de la poire. Le sucré habite le brun. La goutte verte a séché au col. Le sac a pris la forme de la poire, grain au col.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le sac a failli se déchirer jusqu'au fond. Mila reste au bord, les yeux sur la tache. Tu as regardé le col. Oui. Le sac a pris la forme de la poire. Le sucré habite le brun. La goutte verte a séché au col. Le sac a pris la forme de la poire, &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; au col.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le sac a failli se déchirer jusqu'au fond. Mila reste au bord, les yeux sur la tache. Tu as regardé le col. Oui. Le sac a pris la forme de la poire. Le sucré habite le brun. La goutte verte a séché au col. Le sac a pris la forme de la poire, grain au col.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le sac a failli se déchirer jusqu'au fond. Mila reste au bord, les yeux sur la tache. Tu as regardé le col. Oui. Le sac a pris la forme de la poire. Le sucré habite le brun. La goutte verte a séché au col. Le sac a pris la forme de la poire, &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; au col.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -15097,7 +15102,7 @@
 papa|Le sac a pris la forme de la poire.
 maman|Le sucré habite le brun.
 narrateur|La goutte verte a séché au col.
-narrateur|Le sac a pris la forme de la poire, grain au col.</t>
+narrateur|Le sac a pris la forme de la poire, grain de cannelle au col.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
@@ -15312,17 +15317,17 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Mila revient, les mains hors des poches. Maintenant ? Oui, le sac est là. Elle s'approche du papier. Vous avez pris le temps. Le papier l'attendait, lourd. La goutte verte a quitté le brun. Le papier attend, grain brun sur le brun.</t>
+          <t>Mila revient, les mains hors des poches. Maintenant ? Oui, le sac est là. Elle s'approche du papier. Vous avez pris le temps. Le papier l'attendait, lourd. La goutte verte a quitté le brun. Le papier attend, grain de cannelle brun sur le brun.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Mila revient, les mains hors des poches. Maintenant ? Oui, le sac est là. Elle s'approche du papier. Vous avez pris le temps. Le papier l'attendait, lourd. La goutte verte a quitté le brun. Le papier attend, grain brun sur le brun.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Mila revient, les mains hors des poches. Maintenant ? Oui, le sac est là. Elle s'approche du papier. Vous avez pris le temps. Le papier l'attendait, lourd. La goutte verte a quitté le brun. Le papier attend, &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; brun sur le brun.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Mila revient, les mains hors des poches. Maintenant ? Oui, le sac est là. Elle s'approche du papier. Vous avez pris le temps. Le papier l'attendait, lourd. La goutte verte a quitté le brun. Le papier attend, grain brun sur le brun.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Mila revient, les mains hors des poches. Maintenant ? Oui, le sac est là. Elle s'approche du papier. Vous avez pris le temps. Le papier l'attendait, lourd. La goutte verte a quitté le brun. Le papier attend, &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; brun sur le brun.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -15467,7 +15472,7 @@
 papa|Vous avez pris le temps.
 maman|Le papier l'attendait, lourd.
 narrateur|La goutte verte a quitté le brun.
-narrateur|Le papier attend, grain brun sur le brun.</t>
+narrateur|Le papier attend, grain de cannelle brun sur le brun.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
@@ -15682,17 +15687,17 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>La poire a failli fendre le sac. On l'a portée. Le stand est à nous. Vous avez offert le fruit. Le sac penche, puis tient. La goutte verte a séché au fond. Le bois de l'étal redevient sec. Le sac penche, puis tient, grain au fond.</t>
+          <t>La poire a failli fendre le sac. On l'a portée. Le stand est à nous. Vous avez offert le fruit. Le sac penche, puis tient. La goutte verte a séché au fond. Le bois de l'étal redevient sec. Le sac penche, puis tient, grain de cannelle au fond.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La poire a failli fendre le sac. On l'a portée. Le stand est à nous. Vous avez offert le fruit. Le sac penche, puis tient. La goutte verte a séché au fond. Le bois de l'étal redevient sec. Le sac penche, puis tient, grain au fond.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La poire a failli fendre le sac. On l'a portée. Le stand est à nous. Vous avez offert le fruit. Le sac penche, puis tient. La goutte verte a séché au fond. Le bois de l'étal redevient sec. Le sac penche, puis tient, &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; au fond.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La poire a failli fendre le sac. On l'a portée. Le stand est à nous. Vous avez offert le fruit. Le sac penche, puis tient. La goutte verte a séché au fond. Le bois de l'étal redevient sec. Le sac penche, puis tient, grain au fond.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La poire a failli fendre le sac. On l'a portée. Le stand est à nous. Vous avez offert le fruit. Le sac penche, puis tient. La goutte verte a séché au fond. Le bois de l'étal redevient sec. Le sac penche, puis tient, &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; au fond.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -15837,7 +15842,7 @@
 maman|Le sac penche, puis tient.
 narrateur|La goutte verte a séché au fond.
 narrateur|Le bois de l'étal redevient sec.
-narrateur|Le sac penche, puis tient, grain au fond.</t>
+narrateur|Le sac penche, puis tient, grain de cannelle au fond.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
@@ -16442,17 +16447,17 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>La tour a failli cacher toutes les poires. Mila reste au bord, les yeux sur le bas. Tu as regardé en bas. Oui. Les poires d'en bas restent à hauteur. La petite a gardé sa joue. La goutte verte a séché sur la planche. Les poires d'en bas restent à hauteur, grain sur la plus petite.</t>
+          <t>La tour a failli cacher toutes les poires. Mila reste au bord, les yeux sur le bas. Tu as regardé en bas. Oui. Les poires d'en bas restent à hauteur. La petite a gardé sa joue. La goutte verte a séché sur la planche. Les poires d'en bas restent à hauteur, grain de cannelle sur la plus petite.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La tour a failli cacher toutes les poires. Mila reste au bord, les yeux sur le bas. Tu as regardé en bas. Oui. Les poires d'en bas restent à hauteur. La petite a gardé sa joue. La goutte verte a séché sur la planche. Les poires d'en bas restent à hauteur, grain sur la plus petite.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La tour a failli cacher toutes les poires. Mila reste au bord, les yeux sur le bas. Tu as regardé en bas. Oui. Les poires d'en bas restent à hauteur. La petite a gardé sa joue. La goutte verte a séché sur la planche. Les poires d'en bas restent à hauteur, &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; sur la plus petite.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La tour a failli cacher toutes les poires. Mila reste au bord, les yeux sur le bas. Tu as regardé en bas. Oui. Les poires d'en bas restent à hauteur. La petite a gardé sa joue. La goutte verte a séché sur la planche. Les poires d'en bas restent à hauteur, grain sur la plus petite.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La tour a failli cacher toutes les poires. Mila reste au bord, les yeux sur le bas. Tu as regardé en bas. Oui. Les poires d'en bas restent à hauteur. La petite a gardé sa joue. La goutte verte a séché sur la planche. Les poires d'en bas restent à hauteur, &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; sur la plus petite.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -16597,7 +16602,7 @@
 papa|Les poires d'en bas restent à hauteur.
 maman|La petite a gardé sa joue.
 narrateur|La goutte verte a séché sur la planche.
-narrateur|Les poires d'en bas restent à hauteur, grain sur la plus petite.</t>
+narrateur|Les poires d'en bas restent à hauteur, grain de cannelle sur la plus petite.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
@@ -16812,17 +16817,17 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Mila revient, une main sur le bord de l'étal. Maintenant ? Oui, ta poire est là. Elle s'approche de la caisse. Vous avez pris le temps. La petite l'attendait. La goutte verte a quitté le bord. Une poire du bas attend, grain sur sa joue.</t>
+          <t>Mila revient, une main sur le bord de l'étal. Maintenant ? Oui, ta poire est là. Elle s'approche de la caisse. Vous avez pris le temps. La petite l'attendait. La goutte verte a quitté le bord. Une poire du bas attend, grain de cannelle sur sa joue.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Mila revient, une main sur le bord de l'étal. Maintenant ? Oui, ta poire est là. Elle s'approche de la caisse. Vous avez pris le temps. La petite l'attendait. La goutte verte a quitté le bord. Une poire du bas attend, grain sur sa joue.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Mila revient, une main sur le bord de l'étal. Maintenant ? Oui, ta poire est là. Elle s'approche de la caisse. Vous avez pris le temps. La petite l'attendait. La goutte verte a quitté le bord. Une poire du bas attend, &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; sur sa joue.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Mila revient, une main sur le bord de l'étal. Maintenant ? Oui, ta poire est là. Elle s'approche de la caisse. Vous avez pris le temps. La petite l'attendait. La goutte verte a quitté le bord. Une poire du bas attend, grain sur sa joue.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Mila revient, une main sur le bord de l'étal. Maintenant ? Oui, ta poire est là. Elle s'approche de la caisse. Vous avez pris le temps. La petite l'attendait. La goutte verte a quitté le bord. Une poire du bas attend, &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; sur sa joue.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
@@ -16967,7 +16972,7 @@
 papa|Vous avez pris le temps.
 maman|La petite l'attendait.
 narrateur|La goutte verte a quitté le bord.
-narrateur|Une poire du bas attend, grain sur sa joue.</t>
+narrateur|Une poire du bas attend, grain de cannelle sur sa joue.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
@@ -17182,17 +17187,17 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>La poire d'en haut a failli tout cacher. On l'a prise, en bas. Le stand est à nous. Vous avez offert le fruit. La poire d'en bas a trouvé sa place. La goutte verte a séché sur sa joue. Le bois de l'étal redevient sec. La poire d'en bas a trouvé sa place, grain voyageur.</t>
+          <t>La poire d'en haut a failli tout cacher. On l'a prise, en bas. Le stand est à nous. Vous avez offert le fruit. La poire d'en bas a trouvé sa place. La goutte verte a séché sur sa joue. Le bois de l'étal redevient sec. La poire d'en bas a trouvé sa place, grain de cannelle voyageur.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La poire d'en haut a failli tout cacher. On l'a prise, en bas. Le stand est à nous. Vous avez offert le fruit. La poire d'en bas a trouvé sa place. La goutte verte a séché sur sa joue. Le bois de l'étal redevient sec. La poire d'en bas a trouvé sa place, grain voyageur.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La poire d'en haut a failli tout cacher. On l'a prise, en bas. Le stand est à nous. Vous avez offert le fruit. La poire d'en bas a trouvé sa place. La goutte verte a séché sur sa joue. Le bois de l'étal redevient sec. La poire d'en bas a trouvé sa place, &lt;emphasis level="moderate"&gt;grain de cannelle&lt;/emphasis&gt; voyageur.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La poire d'en haut a failli tout cacher. On l'a prise, en bas. Le stand est à nous. Vous avez offert le fruit. La poire d'en bas a trouvé sa place. La goutte verte a séché sur sa joue. Le bois de l'étal redevient sec. La poire d'en bas a trouvé sa place, grain voyageur.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La poire d'en haut a failli tout cacher. On l'a prise, en bas. Le stand est à nous. Vous avez offert le fruit. La poire d'en bas a trouvé sa place. La goutte verte a séché sur sa joue. Le bois de l'étal redevient sec. La poire d'en bas a trouvé sa place, &lt;emphasis&gt;grain de cannelle&lt;/emphasis&gt; voyageur.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr"/>
@@ -17337,7 +17342,7 @@
 maman|La poire d'en bas a trouvé sa place.
 narrateur|La goutte verte a séché sur sa joue.
 narrateur|Le bois de l'étal redevient sec.
-narrateur|La poire d'en bas a trouvé sa place, grain voyageur.</t>
+narrateur|La poire d'en bas a trouvé sa place, grain de cannelle voyageur.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
@@ -17363,7 +17368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17434,6 +17439,13 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
